--- a/data/passing-prop-predictions-2025.xlsx
+++ b/data/passing-prop-predictions-2025.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/98038a0616e2a1bf/Desktop/Development/Projects/nfl-prop-model-2/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="35" documentId="11_4C713F7978A890F6D55B6BC366FE3CE5622E443B" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4F427658-3ED2-49DC-9B7C-2F79ACADB2EB}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="11_04E55082DCEDC07E2FDAD079445BB426E960B561" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{324E5CDE-CF0A-4F50-9E2E-CAFDAF0F1BB4}"/>
   <bookViews>
-    <workbookView xWindow="-90" yWindow="-90" windowWidth="19380" windowHeight="10260" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-90" yWindow="-90" windowWidth="19380" windowHeight="10260" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Week 1" sheetId="1" r:id="rId1"/>
@@ -19,13 +19,14 @@
     <sheet name="Week 4" sheetId="4" r:id="rId4"/>
     <sheet name="Week 5" sheetId="5" r:id="rId5"/>
     <sheet name="Week 6" sheetId="6" r:id="rId6"/>
+    <sheet name="Week 7" sheetId="7" r:id="rId7"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1189" uniqueCount="284">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1237" uniqueCount="280">
   <si>
     <t>Player</t>
   </si>
@@ -81,6 +82,9 @@
     <t>150</t>
   </si>
   <si>
+    <t>94.3%</t>
+  </si>
+  <si>
     <t>OVER</t>
   </si>
   <si>
@@ -97,6 +101,9 @@
   </si>
   <si>
     <t>298</t>
+  </si>
+  <si>
+    <t>30.5%</t>
   </si>
   <si>
     <t>UNDER</t>
@@ -120,6 +127,9 @@
     <t>209</t>
   </si>
   <si>
+    <t>31.2%</t>
+  </si>
+  <si>
     <t>J.Flacco</t>
   </si>
   <si>
@@ -132,7 +142,7 @@
     <t>290</t>
   </si>
   <si>
-    <t>48.9%</t>
+    <t>57.4%</t>
   </si>
   <si>
     <t>C.Williams</t>
@@ -147,6 +157,9 @@
     <t>210</t>
   </si>
   <si>
+    <t>40.8%</t>
+  </si>
+  <si>
     <t>G.Smith</t>
   </si>
   <si>
@@ -157,6 +170,9 @@
   </si>
   <si>
     <t>362</t>
+  </si>
+  <si>
+    <t>52.4%</t>
   </si>
   <si>
     <t>T.Lawrence</t>
@@ -171,10 +187,16 @@
     <t>178</t>
   </si>
   <si>
+    <t>27.5%</t>
+  </si>
+  <si>
     <t>D.Maye</t>
   </si>
   <si>
     <t>287</t>
+  </si>
+  <si>
+    <t>26.1%</t>
   </si>
   <si>
     <t>J.Herbert</t>
@@ -189,7 +211,7 @@
     <t>318</t>
   </si>
   <si>
-    <t>67.2%</t>
+    <t>60.2%</t>
   </si>
   <si>
     <t>J.Hurts</t>
@@ -204,6 +226,9 @@
     <t>152</t>
   </si>
   <si>
+    <t>45.8%</t>
+  </si>
+  <si>
     <t>J.Love</t>
   </si>
   <si>
@@ -216,6 +241,9 @@
     <t>188</t>
   </si>
   <si>
+    <t>39.6%</t>
+  </si>
+  <si>
     <t>C.Stroud</t>
   </si>
   <si>
@@ -223,6 +251,9 @@
   </si>
   <si>
     <t>LA</t>
+  </si>
+  <si>
+    <t>41.0%</t>
   </si>
   <si>
     <t>J.Fields</t>
@@ -237,10 +268,16 @@
     <t>218</t>
   </si>
   <si>
+    <t>57.5%</t>
+  </si>
+  <si>
     <t>B.Young</t>
   </si>
   <si>
     <t>154</t>
+  </si>
+  <si>
+    <t>55.0%</t>
   </si>
   <si>
     <t>J.Daniels</t>
@@ -255,7 +292,7 @@
     <t>233</t>
   </si>
   <si>
-    <t>64.3%</t>
+    <t>61.1%</t>
   </si>
   <si>
     <t>J.Burrow</t>
@@ -264,7 +301,7 @@
     <t>113</t>
   </si>
   <si>
-    <t>67.5%</t>
+    <t>63.0%</t>
   </si>
   <si>
     <t>M.Stafford</t>
@@ -273,10 +310,16 @@
     <t>245</t>
   </si>
   <si>
+    <t>43.3%</t>
+  </si>
+  <si>
     <t>P.Mahomes</t>
   </si>
   <si>
     <t>258</t>
+  </si>
+  <si>
+    <t>46.7%</t>
   </si>
   <si>
     <t>K.Murray</t>
@@ -291,7 +334,7 @@
     <t>163</t>
   </si>
   <si>
-    <t>70.5%</t>
+    <t>79.3%</t>
   </si>
   <si>
     <t>J.Goff</t>
@@ -300,10 +343,16 @@
     <t>225</t>
   </si>
   <si>
+    <t>78.5%</t>
+  </si>
+  <si>
     <t>J.Allen</t>
   </si>
   <si>
     <t>394</t>
+  </si>
+  <si>
+    <t>47.3%</t>
   </si>
   <si>
     <t>T.Tagovailoa</t>
@@ -318,6 +367,9 @@
     <t>114</t>
   </si>
   <si>
+    <t>59.3%</t>
+  </si>
+  <si>
     <t>B.Nix</t>
   </si>
   <si>
@@ -330,10 +382,16 @@
     <t>176</t>
   </si>
   <si>
+    <t>75.9%</t>
+  </si>
+  <si>
     <t>B.Mayfield</t>
   </si>
   <si>
     <t>167</t>
+  </si>
+  <si>
+    <t>68.0%</t>
   </si>
   <si>
     <t>R.Wilson</t>
@@ -342,7 +400,7 @@
     <t>168</t>
   </si>
   <si>
-    <t>42.9%</t>
+    <t>44.0%</t>
   </si>
   <si>
     <t>B.Purdy</t>
@@ -351,16 +409,22 @@
     <t>277</t>
   </si>
   <si>
+    <t>59.9%</t>
+  </si>
+  <si>
     <t>S.Rattler</t>
   </si>
   <si>
     <t>214</t>
   </si>
   <si>
-    <t>59.3%</t>
+    <t>64.3%</t>
   </si>
   <si>
     <t>D.Prescott</t>
+  </si>
+  <si>
+    <t>39.7%</t>
   </si>
   <si>
     <t>D.Jones</t>
@@ -369,148 +433,103 @@
     <t>272</t>
   </si>
   <si>
+    <t>49.7%</t>
+  </si>
+  <si>
     <t>A.Rodgers</t>
   </si>
   <si>
     <t>244</t>
   </si>
   <si>
-    <t>45.8%</t>
+    <t>52.1%</t>
+  </si>
+  <si>
+    <t>18/30</t>
+  </si>
+  <si>
+    <t>315</t>
+  </si>
+  <si>
+    <t>56.3%</t>
+  </si>
+  <si>
+    <t>295</t>
   </si>
   <si>
     <t>68.7%</t>
   </si>
   <si>
-    <t>43.0%</t>
+    <t>101</t>
   </si>
   <si>
-    <t>53.8%</t>
-  </si>
-  <si>
-    <t>18/30</t>
-  </si>
-  <si>
-    <t>94.3%</t>
-  </si>
-  <si>
-    <t>30.5%</t>
-  </si>
-  <si>
-    <t>31.2%</t>
-  </si>
-  <si>
-    <t>57.4%</t>
-  </si>
-  <si>
-    <t>40.8%</t>
-  </si>
-  <si>
-    <t>52.4%</t>
-  </si>
-  <si>
-    <t>27.5%</t>
-  </si>
-  <si>
-    <t>26.1%</t>
-  </si>
-  <si>
-    <t>60.2%</t>
-  </si>
-  <si>
-    <t>39.6%</t>
-  </si>
-  <si>
-    <t>41.0%</t>
-  </si>
-  <si>
-    <t>57.5%</t>
-  </si>
-  <si>
-    <t>55.0%</t>
-  </si>
-  <si>
-    <t>61.1%</t>
-  </si>
-  <si>
-    <t>63.0%</t>
-  </si>
-  <si>
-    <t>43.3%</t>
-  </si>
-  <si>
-    <t>46.7%</t>
-  </si>
-  <si>
-    <t>79.3%</t>
-  </si>
-  <si>
-    <t>78.5%</t>
-  </si>
-  <si>
-    <t>47.3%</t>
-  </si>
-  <si>
-    <t>75.9%</t>
-  </si>
-  <si>
-    <t>68.0%</t>
-  </si>
-  <si>
-    <t>44.0%</t>
-  </si>
-  <si>
-    <t>59.9%</t>
-  </si>
-  <si>
-    <t>39.7%</t>
-  </si>
-  <si>
-    <t>49.7%</t>
-  </si>
-  <si>
-    <t>52.1%</t>
-  </si>
-  <si>
-    <t>315</t>
-  </si>
-  <si>
-    <t>295</t>
-  </si>
-  <si>
-    <t>101</t>
+    <t>55.6%</t>
   </si>
   <si>
     <t>242</t>
   </si>
   <si>
+    <t>44.1%</t>
+  </si>
+  <si>
     <t>207</t>
+  </si>
+  <si>
+    <t>45.1%</t>
   </si>
   <si>
     <t>203</t>
   </si>
   <si>
+    <t>34.8%</t>
+  </si>
+  <si>
     <t>334</t>
+  </si>
+  <si>
+    <t>62.6%</t>
   </si>
   <si>
     <t>361</t>
   </si>
   <si>
+    <t>35.2%</t>
+  </si>
+  <si>
     <t>199</t>
+  </si>
+  <si>
+    <t>46.4%</t>
   </si>
   <si>
     <t>215</t>
   </si>
   <si>
-    <t>52.5%</t>
+    <t>65.4%</t>
+  </si>
+  <si>
+    <t>57.9%</t>
   </si>
   <si>
     <t>292</t>
   </si>
   <si>
+    <t>42.9%</t>
+  </si>
+  <si>
     <t>27</t>
   </si>
   <si>
+    <t>47.4%</t>
+  </si>
+  <si>
     <t>187</t>
+  </si>
+  <si>
+    <t>47.1%</t>
+  </si>
+  <si>
+    <t>51.0%</t>
   </si>
   <si>
     <t>180</t>
@@ -519,13 +538,25 @@
     <t>328</t>
   </si>
   <si>
+    <t>54.6%</t>
+  </si>
+  <si>
     <t>230</t>
+  </si>
+  <si>
+    <t>33.4%</t>
   </si>
   <si>
     <t>271</t>
   </si>
   <si>
+    <t>38.0%</t>
+  </si>
+  <si>
     <t>316</t>
+  </si>
+  <si>
+    <t>57.0%</t>
   </si>
   <si>
     <t>M.Jones</t>
@@ -534,97 +565,40 @@
     <t>279</t>
   </si>
   <si>
+    <t>75.1%</t>
+  </si>
+  <si>
     <t>148</t>
   </si>
   <si>
-    <t>56.8%</t>
+    <t>68.5%</t>
   </si>
   <si>
     <t>220</t>
   </si>
   <si>
+    <t>76.3%</t>
+  </si>
+  <si>
     <t>206</t>
   </si>
   <si>
-    <t>49.1%</t>
+    <t>60.0%</t>
   </si>
   <si>
     <t>450</t>
   </si>
   <si>
+    <t>43.4%</t>
+  </si>
+  <si>
     <t>200</t>
   </si>
   <si>
-    <t>62.6%</t>
+    <t>76.1%</t>
   </si>
   <si>
-    <t>56.3%</t>
-  </si>
-  <si>
-    <t>55.6%</t>
-  </si>
-  <si>
-    <t>59.6%</t>
-  </si>
-  <si>
-    <t>44.1%</t>
-  </si>
-  <si>
-    <t>45.1%</t>
-  </si>
-  <si>
-    <t>34.8%</t>
-  </si>
-  <si>
-    <t>35.2%</t>
-  </si>
-  <si>
-    <t>46.4%</t>
-  </si>
-  <si>
-    <t>65.4%</t>
-  </si>
-  <si>
-    <t>57.9%</t>
-  </si>
-  <si>
-    <t>47.4%</t>
-  </si>
-  <si>
-    <t>47.1%</t>
-  </si>
-  <si>
-    <t>51.0%</t>
-  </si>
-  <si>
-    <t>54.6%</t>
-  </si>
-  <si>
-    <t>33.4%</t>
-  </si>
-  <si>
-    <t>38.0%</t>
-  </si>
-  <si>
-    <t>57.0%</t>
-  </si>
-  <si>
-    <t>75.1%</t>
-  </si>
-  <si>
-    <t>68.5%</t>
-  </si>
-  <si>
-    <t>76.3%</t>
-  </si>
-  <si>
-    <t>60.0%</t>
-  </si>
-  <si>
-    <t>43.4%</t>
-  </si>
-  <si>
-    <t>76.1%</t>
+    <t>52.5%</t>
   </si>
   <si>
     <t>15/28</t>
@@ -633,55 +607,94 @@
     <t>146</t>
   </si>
   <si>
+    <t>44.6%</t>
+  </si>
+  <si>
     <t>213</t>
+  </si>
+  <si>
+    <t>52.8%</t>
   </si>
   <si>
     <t>142</t>
   </si>
   <si>
-    <t>52.8%</t>
+    <t>54.5%</t>
   </si>
   <si>
     <t>183</t>
   </si>
   <si>
+    <t>37.3%</t>
+  </si>
+  <si>
     <t>226</t>
   </si>
   <si>
-    <t>70.0%</t>
+    <t>67.3%</t>
   </si>
   <si>
     <t>196</t>
   </si>
   <si>
+    <t>67.2%</t>
+  </si>
+  <si>
     <t>204</t>
+  </si>
+  <si>
+    <t>41.6%</t>
   </si>
   <si>
     <t>222</t>
   </si>
   <si>
+    <t>39.2%</t>
+  </si>
+  <si>
     <t>251</t>
+  </si>
+  <si>
+    <t>42.2%</t>
+  </si>
+  <si>
+    <t>32.5%</t>
   </si>
   <si>
     <t>224</t>
   </si>
   <si>
+    <t>53.8%</t>
+  </si>
+  <si>
     <t>160</t>
+  </si>
+  <si>
+    <t>57.2%</t>
   </si>
   <si>
     <t>288</t>
   </si>
   <si>
+    <t>63.4%</t>
+  </si>
+  <si>
     <t>202</t>
+  </si>
+  <si>
+    <t>55.5%</t>
   </si>
   <si>
     <t>139</t>
   </si>
   <si>
-    <t>44.6%</t>
+    <t>40.5%</t>
   </si>
   <si>
     <t>268</t>
+  </si>
+  <si>
+    <t>30.8%</t>
   </si>
   <si>
     <t>T.Taylor</t>
@@ -690,19 +703,37 @@
     <t>197</t>
   </si>
   <si>
-    <t>42.2%</t>
+    <t>47.9%</t>
+  </si>
+  <si>
+    <t>43.0%</t>
   </si>
   <si>
     <t>300</t>
   </si>
   <si>
+    <t>48.0%</t>
+  </si>
+  <si>
     <t>153</t>
+  </si>
+  <si>
+    <t>63.8%</t>
+  </si>
+  <si>
+    <t>56.8%</t>
   </si>
   <si>
     <t>159</t>
   </si>
   <si>
+    <t>70.0%</t>
+  </si>
+  <si>
     <t>284</t>
+  </si>
+  <si>
+    <t>70.7%</t>
   </si>
   <si>
     <t>J.Browning</t>
@@ -711,76 +742,19 @@
     <t>140</t>
   </si>
   <si>
+    <t>49.1%</t>
+  </si>
+  <si>
     <t>C.Wentz</t>
   </si>
   <si>
     <t>173</t>
   </si>
   <si>
-    <t>13/26</t>
-  </si>
-  <si>
-    <t>54.5%</t>
-  </si>
-  <si>
-    <t>37.3%</t>
-  </si>
-  <si>
-    <t>67.3%</t>
-  </si>
-  <si>
-    <t>41.6%</t>
-  </si>
-  <si>
-    <t>39.2%</t>
-  </si>
-  <si>
-    <t>32.5%</t>
-  </si>
-  <si>
-    <t>57.2%</t>
-  </si>
-  <si>
-    <t>63.4%</t>
-  </si>
-  <si>
-    <t>55.5%</t>
-  </si>
-  <si>
-    <t>40.5%</t>
-  </si>
-  <si>
-    <t>30.8%</t>
-  </si>
-  <si>
-    <t>47.9%</t>
-  </si>
-  <si>
-    <t>48.0%</t>
-  </si>
-  <si>
-    <t>63.8%</t>
-  </si>
-  <si>
-    <t>70.7%</t>
-  </si>
-  <si>
     <t>50.5%</t>
   </si>
   <si>
-    <t>48.5%</t>
-  </si>
-  <si>
-    <t>62.4%</t>
-  </si>
-  <si>
-    <t>63.3%</t>
-  </si>
-  <si>
-    <t>73.5%</t>
-  </si>
-  <si>
-    <t>64.4%</t>
+    <t>13/26</t>
   </si>
   <si>
     <t>67.0%</t>
@@ -810,7 +784,19 @@
     <t>51.6%</t>
   </si>
   <si>
+    <t>64.4%</t>
+  </si>
+  <si>
+    <t>62.4%</t>
+  </si>
+  <si>
+    <t>48.9%</t>
+  </si>
+  <si>
     <t>72.9%</t>
+  </si>
+  <si>
+    <t>48.5%</t>
   </si>
   <si>
     <t>49.5%</t>
@@ -820,6 +806,9 @@
   </si>
   <si>
     <t>42.1%</t>
+  </si>
+  <si>
+    <t>67.5%</t>
   </si>
   <si>
     <t>60.6%</t>
@@ -840,13 +829,25 @@
     <t>61.9%</t>
   </si>
   <si>
+    <t>63.3%</t>
+  </si>
+  <si>
+    <t>70.5%</t>
+  </si>
+  <si>
     <t>63.1%</t>
   </si>
   <si>
     <t>52.7%</t>
   </si>
   <si>
+    <t>59.6%</t>
+  </si>
+  <si>
     <t>C.Rush</t>
+  </si>
+  <si>
+    <t>73.5%</t>
   </si>
   <si>
     <t>45.0%</t>
@@ -864,26 +865,14 @@
     <t>58.5%</t>
   </si>
   <si>
-    <t>Mean Pred</t>
-  </si>
-  <si>
-    <t>Vegas Line</t>
-  </si>
-  <si>
-    <t>Prob Over</t>
-  </si>
-  <si>
-    <t>W/L</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> </t>
+    <t>40.7%</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -895,28 +884,20 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
-      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <name val="Calibri"/>
     </font>
     <font>
       <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
-      <family val="2"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -947,6 +928,18 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFB6C1"/>
+        <bgColor rgb="FFFFB6C1"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF90EE90"/>
+        <bgColor rgb="FF90EE90"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -960,7 +953,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -981,23 +974,29 @@
     <xf numFmtId="16" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="10" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1223,7 +1222,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-6916-4B0D-8BAF-8D66A80A2C18}"/>
+              <c16:uniqueId val="{00000000-468D-4FDC-8D47-23D4A658F5FA}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1402,7 +1401,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-6916-4B0D-8BAF-8D66A80A2C18}"/>
+              <c16:uniqueId val="{00000001-468D-4FDC-8D47-23D4A658F5FA}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1539,10 +1538,6 @@
     <xdr:clientData/>
   </xdr:oneCellAnchor>
 </xdr:wsDr>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1911,13 +1906,13 @@
         <v>17</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>121</v>
+        <v>18</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K2" s="1">
         <v>168.2</v>
@@ -1931,13 +1926,13 @@
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.75">
       <c r="A3" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>16</v>
@@ -1949,16 +1944,16 @@
         <v>249.5</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>122</v>
+        <v>25</v>
       </c>
       <c r="I3" s="4" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="K3" s="1">
         <v>144.5</v>
@@ -1972,16 +1967,16 @@
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.75">
       <c r="A4" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="E4" s="1">
         <v>220</v>
@@ -1990,16 +1985,16 @@
         <v>249.5</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>123</v>
+        <v>33</v>
       </c>
       <c r="I4" s="4" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K4" s="1">
         <v>144.1</v>
@@ -2013,13 +2008,13 @@
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.75">
       <c r="A5" s="1" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="D5" s="1" t="s">
         <v>16</v>
@@ -2031,16 +2026,16 @@
         <v>218.5</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>124</v>
+        <v>38</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K5" s="1">
         <v>153.80000000000001</v>
@@ -2054,13 +2049,13 @@
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.75">
       <c r="A6" s="1" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="D6" s="1" t="s">
         <v>16</v>
@@ -2072,16 +2067,16 @@
         <v>230.5</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>125</v>
+        <v>43</v>
       </c>
       <c r="I6" s="4" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="J6" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K6" s="1">
         <v>139.5</v>
@@ -2095,16 +2090,16 @@
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.75">
       <c r="A7" s="1" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="E7" s="1">
         <v>218.10000610351599</v>
@@ -2113,16 +2108,16 @@
         <v>215.5</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>126</v>
+        <v>48</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J7" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K7" s="1">
         <v>143.1</v>
@@ -2136,13 +2131,13 @@
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.75">
       <c r="A8" s="1" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="D8" s="1" t="s">
         <v>16</v>
@@ -2154,16 +2149,16 @@
         <v>247.5</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>127</v>
+        <v>53</v>
       </c>
       <c r="I8" s="4" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="J8" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K8" s="1">
         <v>136.5</v>
@@ -2177,13 +2172,13 @@
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.75">
       <c r="A9" s="1" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="D9" s="1" t="s">
         <v>16</v>
@@ -2195,16 +2190,16 @@
         <v>223.5</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>128</v>
+        <v>56</v>
       </c>
       <c r="I9" s="4" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="J9" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="K9" s="1">
         <v>110.4</v>
@@ -2218,13 +2213,13 @@
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.75">
       <c r="A10" s="1" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>16</v>
@@ -2236,16 +2231,16 @@
         <v>239.5</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>129</v>
+        <v>61</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J10" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K10" s="1">
         <v>179</v>
@@ -2259,13 +2254,13 @@
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.75">
       <c r="A11" s="1" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="D11" s="1" t="s">
         <v>16</v>
@@ -2277,16 +2272,16 @@
         <v>223.5</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>116</v>
+        <v>66</v>
       </c>
       <c r="I11" s="4" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="J11" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K11" s="1">
         <v>141.6</v>
@@ -2300,13 +2295,13 @@
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.75">
       <c r="A12" s="1" t="s">
-        <v>59</v>
+        <v>67</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="D12" s="1" t="s">
         <v>16</v>
@@ -2318,16 +2313,16 @@
         <v>240.5</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>62</v>
+        <v>70</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>130</v>
+        <v>71</v>
       </c>
       <c r="I12" s="4" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="J12" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K12" s="1">
         <v>149.9</v>
@@ -2341,16 +2336,16 @@
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.75">
       <c r="A13" s="1" t="s">
-        <v>63</v>
+        <v>72</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>64</v>
+        <v>73</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>65</v>
+        <v>74</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="E13" s="1">
         <v>212.80000305175801</v>
@@ -2359,16 +2354,16 @@
         <v>226.5</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>62</v>
+        <v>70</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>131</v>
+        <v>75</v>
       </c>
       <c r="I13" s="4" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="J13" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K13" s="1">
         <v>136.30000000000001</v>
@@ -2382,13 +2377,13 @@
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.75">
       <c r="A14" s="1" t="s">
-        <v>66</v>
+        <v>76</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>67</v>
+        <v>77</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>68</v>
+        <v>78</v>
       </c>
       <c r="D14" s="1" t="s">
         <v>16</v>
@@ -2400,16 +2395,16 @@
         <v>171.5</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>132</v>
+        <v>80</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J14" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K14" s="1">
         <v>107.6</v>
@@ -2423,16 +2418,16 @@
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.75">
       <c r="A15" s="1" t="s">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="E15" s="1">
         <v>227.5</v>
@@ -2441,16 +2436,16 @@
         <v>220.5</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>71</v>
+        <v>82</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>133</v>
+        <v>83</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J15" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="K15" s="1">
         <v>152.19999999999999</v>
@@ -2464,13 +2459,13 @@
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.75">
       <c r="A16" s="1" t="s">
-        <v>72</v>
+        <v>84</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>73</v>
+        <v>85</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>74</v>
+        <v>86</v>
       </c>
       <c r="D16" s="1" t="s">
         <v>16</v>
@@ -2482,16 +2477,16 @@
         <v>230.5</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>75</v>
+        <v>87</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>134</v>
+        <v>88</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J16" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K16" s="1">
         <v>170.8</v>
@@ -2505,16 +2500,16 @@
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.75">
       <c r="A17" s="1" t="s">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="E17" s="1">
         <v>276.39999389648398</v>
@@ -2523,16 +2518,16 @@
         <v>256.5</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>135</v>
+        <v>91</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J17" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="K17" s="1">
         <v>199</v>
@@ -2546,13 +2541,13 @@
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.75">
       <c r="A18" s="1" t="s">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>65</v>
+        <v>74</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>64</v>
+        <v>73</v>
       </c>
       <c r="D18" s="1" t="s">
         <v>16</v>
@@ -2564,16 +2559,16 @@
         <v>240.5</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>136</v>
+        <v>94</v>
       </c>
       <c r="I18" s="4" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="J18" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="K18" s="1">
         <v>155.4</v>
@@ -2587,16 +2582,16 @@
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.75">
       <c r="A19" s="1" t="s">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="E19" s="1">
         <v>250.30000305175801</v>
@@ -2605,16 +2600,16 @@
         <v>255.5</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>83</v>
+        <v>96</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>137</v>
+        <v>97</v>
       </c>
       <c r="I19" s="4" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="J19" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="K19" s="1">
         <v>175.2</v>
@@ -2628,16 +2623,16 @@
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.75">
       <c r="A20" s="1" t="s">
-        <v>84</v>
+        <v>98</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>85</v>
+        <v>99</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>86</v>
+        <v>100</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="E20" s="1">
         <v>262.39999389648398</v>
@@ -2646,16 +2641,16 @@
         <v>215.5</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>87</v>
+        <v>101</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>138</v>
+        <v>102</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J20" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="K20" s="1">
         <v>189.7</v>
@@ -2669,16 +2664,16 @@
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.75">
       <c r="A21" s="1" t="s">
-        <v>89</v>
+        <v>103</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="E21" s="1">
         <v>281.39999389648398</v>
@@ -2687,16 +2682,16 @@
         <v>234.5</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>90</v>
+        <v>104</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>139</v>
+        <v>105</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J21" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="K21" s="1">
         <v>203.7</v>
@@ -2710,13 +2705,13 @@
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.75">
       <c r="A22" s="1" t="s">
-        <v>91</v>
+        <v>106</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D22" s="1" t="s">
         <v>16</v>
@@ -2728,16 +2723,16 @@
         <v>240.5</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>92</v>
+        <v>107</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>140</v>
+        <v>108</v>
       </c>
       <c r="I22" s="4" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="J22" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="K22" s="1">
         <v>159.19999999999999</v>
@@ -2751,16 +2746,16 @@
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.75">
       <c r="A23" s="1" t="s">
-        <v>93</v>
+        <v>109</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>94</v>
+        <v>110</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>95</v>
+        <v>111</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="E23" s="1">
         <v>267.79998779296898</v>
@@ -2769,16 +2764,16 @@
         <v>255.5</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>96</v>
+        <v>112</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J23" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="K23" s="1">
         <v>193</v>
@@ -2792,13 +2787,13 @@
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.75">
       <c r="A24" s="1" t="s">
-        <v>97</v>
+        <v>114</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>98</v>
+        <v>115</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>99</v>
+        <v>116</v>
       </c>
       <c r="D24" s="1" t="s">
         <v>16</v>
@@ -2810,16 +2805,16 @@
         <v>210.5</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>100</v>
+        <v>117</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>141</v>
+        <v>118</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J24" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="K24" s="1">
         <v>177.1</v>
@@ -2833,16 +2828,16 @@
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.75">
       <c r="A25" s="1" t="s">
-        <v>101</v>
+        <v>119</v>
       </c>
       <c r="B25" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C25" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="C25" s="1" t="s">
-        <v>21</v>
-      </c>
       <c r="D25" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="E25" s="1">
         <v>265.10000610351602</v>
@@ -2851,16 +2846,16 @@
         <v>237.5</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>102</v>
+        <v>120</v>
       </c>
       <c r="H25" s="1" t="s">
-        <v>142</v>
+        <v>121</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J25" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="K25" s="1">
         <v>190.3</v>
@@ -2874,16 +2869,16 @@
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.75">
       <c r="A26" s="1" t="s">
-        <v>103</v>
+        <v>122</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>74</v>
+        <v>86</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>73</v>
+        <v>85</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="E26" s="1">
         <v>213.89999389648401</v>
@@ -2892,16 +2887,16 @@
         <v>222.5</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>104</v>
+        <v>123</v>
       </c>
       <c r="H26" s="1" t="s">
-        <v>143</v>
+        <v>124</v>
       </c>
       <c r="I26" s="4" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="J26" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K26" s="1">
         <v>137.4</v>
@@ -2915,7 +2910,7 @@
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.75">
       <c r="A27" s="1" t="s">
-        <v>106</v>
+        <v>125</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>15</v>
@@ -2924,7 +2919,7 @@
         <v>14</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="E27" s="1">
         <v>253.80000305175801</v>
@@ -2933,16 +2928,16 @@
         <v>238.5</v>
       </c>
       <c r="G27" s="1" t="s">
-        <v>107</v>
+        <v>126</v>
       </c>
       <c r="H27" s="1" t="s">
-        <v>144</v>
+        <v>127</v>
       </c>
       <c r="I27" s="3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J27" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K27" s="1">
         <v>177.7</v>
@@ -2956,13 +2951,13 @@
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.75">
       <c r="A28" s="1" t="s">
-        <v>108</v>
+        <v>128</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>86</v>
+        <v>100</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>85</v>
+        <v>99</v>
       </c>
       <c r="D28" s="1" t="s">
         <v>16</v>
@@ -2974,16 +2969,16 @@
         <v>186.5</v>
       </c>
       <c r="G28" s="1" t="s">
-        <v>109</v>
+        <v>129</v>
       </c>
       <c r="H28" s="1" t="s">
-        <v>76</v>
+        <v>130</v>
       </c>
       <c r="I28" s="3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J28" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K28" s="1">
         <v>132.5</v>
@@ -2997,16 +2992,16 @@
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.75">
       <c r="A29" s="1" t="s">
-        <v>111</v>
+        <v>131</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="E29" s="1">
         <v>222.69999694824199</v>
@@ -3015,16 +3010,16 @@
         <v>237.5</v>
       </c>
       <c r="G29" s="1" t="s">
-        <v>62</v>
+        <v>70</v>
       </c>
       <c r="H29" s="1" t="s">
-        <v>145</v>
+        <v>132</v>
       </c>
       <c r="I29" s="4" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="J29" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K29" s="1">
         <v>147.5</v>
@@ -3038,13 +3033,13 @@
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.75">
       <c r="A30" s="1" t="s">
-        <v>112</v>
+        <v>133</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>95</v>
+        <v>111</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>94</v>
+        <v>110</v>
       </c>
       <c r="D30" s="1" t="s">
         <v>16</v>
@@ -3056,16 +3051,16 @@
         <v>193.5</v>
       </c>
       <c r="G30" s="1" t="s">
-        <v>113</v>
+        <v>134</v>
       </c>
       <c r="H30" s="1" t="s">
-        <v>146</v>
+        <v>135</v>
       </c>
       <c r="I30" s="3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J30" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K30" s="1">
         <v>117.5</v>
@@ -3079,16 +3074,16 @@
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.75">
       <c r="A31" s="1" t="s">
-        <v>114</v>
+        <v>136</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>68</v>
+        <v>78</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>67</v>
+        <v>77</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="E31" s="1">
         <v>216.69999694824199</v>
@@ -3097,16 +3092,16 @@
         <v>214.5</v>
       </c>
       <c r="G31" s="1" t="s">
-        <v>115</v>
+        <v>137</v>
       </c>
       <c r="H31" s="1" t="s">
-        <v>147</v>
+        <v>138</v>
       </c>
       <c r="I31" s="3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J31" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K31" s="1">
         <v>140.19999999999999</v>
@@ -3118,7 +3113,7 @@
         <v>293.60000000000002</v>
       </c>
       <c r="N31" s="3" t="s">
-        <v>120</v>
+        <v>139</v>
       </c>
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.75">
@@ -3667,7 +3662,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:N89"/>
+  <dimension ref="A1:N85"/>
   <sheetFormatPr defaultColWidth="10.90625" defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -3728,13 +3723,13 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.75">
       <c r="A2" s="1" t="s">
-        <v>93</v>
+        <v>109</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>94</v>
+        <v>110</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>16</v>
@@ -3746,16 +3741,16 @@
         <v>226.5</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>148</v>
+        <v>140</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>177</v>
+        <v>141</v>
       </c>
       <c r="I2" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K2" s="1">
         <v>159</v>
@@ -3775,10 +3770,10 @@
         <v>14</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>68</v>
+        <v>78</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="E3" s="1">
         <v>219.5</v>
@@ -3787,16 +3782,16 @@
         <v>192.5</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>149</v>
+        <v>142</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>117</v>
+        <v>143</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K3" s="1">
         <v>143.19999999999999</v>
@@ -3810,16 +3805,16 @@
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.75">
       <c r="A4" s="1" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="E4" s="1">
         <v>226.30000305175801</v>
@@ -3828,16 +3823,16 @@
         <v>218.5</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>150</v>
+        <v>144</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>178</v>
+        <v>145</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="K4" s="1">
         <v>151.19999999999999</v>
@@ -3851,16 +3846,16 @@
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.75">
       <c r="A5" s="1" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="E5" s="1">
         <v>253.10000610351599</v>
@@ -3869,16 +3864,16 @@
         <v>261.5</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>180</v>
+        <v>147</v>
       </c>
       <c r="I5" s="4" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K5" s="1">
         <v>177.1</v>
@@ -3892,13 +3887,13 @@
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.75">
       <c r="A6" s="1" t="s">
-        <v>63</v>
+        <v>72</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>64</v>
+        <v>73</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D6" s="1" t="s">
         <v>16</v>
@@ -3910,16 +3905,16 @@
         <v>222.5</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>181</v>
+        <v>149</v>
       </c>
       <c r="I6" s="4" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="J6" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K6" s="1">
         <v>136.69999999999999</v>
@@ -3933,10 +3928,10 @@
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.75">
       <c r="A7" s="1" t="s">
-        <v>114</v>
+        <v>136</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>68</v>
+        <v>78</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>14</v>
@@ -3951,16 +3946,16 @@
         <v>235.5</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>182</v>
+        <v>151</v>
       </c>
       <c r="I7" s="4" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="J7" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K7" s="1">
         <v>137.69999999999999</v>
@@ -3974,13 +3969,13 @@
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.75">
       <c r="A8" s="1" t="s">
-        <v>89</v>
+        <v>103</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="D8" s="1" t="s">
         <v>16</v>
@@ -3992,16 +3987,16 @@
         <v>240.5</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>176</v>
+        <v>153</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J8" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K8" s="1">
         <v>184.1</v>
@@ -4015,13 +4010,13 @@
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.75">
       <c r="A9" s="1" t="s">
-        <v>111</v>
+        <v>131</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>74</v>
+        <v>86</v>
       </c>
       <c r="D9" s="1" t="s">
         <v>16</v>
@@ -4033,16 +4028,16 @@
         <v>240.5</v>
       </c>
       <c r="G9" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="H9" s="1" t="s">
         <v>155</v>
       </c>
-      <c r="H9" s="1" t="s">
-        <v>183</v>
-      </c>
       <c r="I9" s="4" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="J9" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="K9" s="1">
         <v>143.6</v>
@@ -4056,16 +4051,16 @@
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.75">
       <c r="A10" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D10" s="1" t="s">
         <v>31</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>29</v>
       </c>
       <c r="E10" s="1">
         <v>245.89999389648401</v>
@@ -4077,13 +4072,13 @@
         <v>156</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>184</v>
+        <v>157</v>
       </c>
       <c r="I10" s="4" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="J10" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K10" s="1">
         <v>169</v>
@@ -4097,16 +4092,16 @@
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.75">
       <c r="A11" s="1" t="s">
-        <v>101</v>
+        <v>119</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>64</v>
+        <v>73</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="E11" s="1">
         <v>248.60000610351599</v>
@@ -4115,16 +4110,16 @@
         <v>225.5</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>185</v>
+        <v>159</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J11" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="K11" s="1">
         <v>173.9</v>
@@ -4138,16 +4133,16 @@
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.75">
       <c r="A12" s="1" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="E12" s="1">
         <v>221.19999694824199</v>
@@ -4156,16 +4151,16 @@
         <v>210.5</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>186</v>
+        <v>160</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J12" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="K12" s="1">
         <v>145.69999999999999</v>
@@ -4179,13 +4174,13 @@
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.75">
       <c r="A13" s="1" t="s">
-        <v>59</v>
+        <v>67</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>73</v>
+        <v>85</v>
       </c>
       <c r="D13" s="1" t="s">
         <v>16</v>
@@ -4197,16 +4192,16 @@
         <v>222.5</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>105</v>
+        <v>162</v>
       </c>
       <c r="I13" s="4" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="J13" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="K13" s="1">
         <v>135.19999999999999</v>
@@ -4220,13 +4215,13 @@
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.75">
       <c r="A14" s="1" t="s">
-        <v>66</v>
+        <v>76</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>67</v>
+        <v>77</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D14" s="1" t="s">
         <v>16</v>
@@ -4238,16 +4233,16 @@
         <v>183.5</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>187</v>
+        <v>164</v>
       </c>
       <c r="I14" s="4" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="J14" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K14" s="1">
         <v>103.4</v>
@@ -4261,13 +4256,13 @@
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.75">
       <c r="A15" s="1" t="s">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="D15" s="1" t="s">
         <v>16</v>
@@ -4279,16 +4274,16 @@
         <v>246.5</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>188</v>
+        <v>166</v>
       </c>
       <c r="I15" s="4" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="J15" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K15" s="1">
         <v>167.4</v>
@@ -4302,10 +4297,10 @@
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.75">
       <c r="A16" s="1" t="s">
-        <v>108</v>
+        <v>128</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>86</v>
+        <v>100</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>15</v>
@@ -4320,16 +4315,16 @@
         <v>208.5</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>189</v>
+        <v>167</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J16" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="K16" s="1">
         <v>135.6</v>
@@ -4343,13 +4338,13 @@
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.75">
       <c r="A17" s="1" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="D17" s="1" t="s">
         <v>16</v>
@@ -4361,16 +4356,16 @@
         <v>240.5</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>162</v>
+        <v>168</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>124</v>
+        <v>38</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J17" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="K17" s="1">
         <v>174.5</v>
@@ -4384,16 +4379,16 @@
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.75">
       <c r="A18" s="1" t="s">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>85</v>
+        <v>99</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="E18" s="1">
         <v>220.60000610351599</v>
@@ -4402,16 +4397,16 @@
         <v>212.5</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>163</v>
+        <v>169</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>190</v>
+        <v>170</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J18" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K18" s="1">
         <v>143.1</v>
@@ -4425,16 +4420,16 @@
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.75">
       <c r="A19" s="1" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>94</v>
+        <v>110</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="E19" s="1">
         <v>201.80000305175801</v>
@@ -4443,16 +4438,16 @@
         <v>226.5</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>164</v>
+        <v>171</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>191</v>
+        <v>172</v>
       </c>
       <c r="I19" s="4" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="J19" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="K19" s="1">
         <v>126.9</v>
@@ -4466,16 +4461,16 @@
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.75">
       <c r="A20" s="1" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="E20" s="1">
         <v>218.89999389648401</v>
@@ -4484,16 +4479,16 @@
         <v>237.5</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>165</v>
+        <v>173</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>192</v>
+        <v>174</v>
       </c>
       <c r="I20" s="4" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="J20" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="K20" s="1">
         <v>141.9</v>
@@ -4507,13 +4502,13 @@
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.75">
       <c r="A21" s="1" t="s">
-        <v>112</v>
+        <v>133</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>95</v>
+        <v>111</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>98</v>
+        <v>115</v>
       </c>
       <c r="D21" s="1" t="s">
         <v>16</v>
@@ -4525,16 +4520,16 @@
         <v>213.5</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>166</v>
+        <v>175</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>193</v>
+        <v>176</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J21" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K21" s="1">
         <v>149.69999999999999</v>
@@ -4548,16 +4543,16 @@
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.75">
       <c r="A22" s="1" t="s">
-        <v>167</v>
+        <v>177</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>15</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>86</v>
+        <v>100</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="E22" s="1">
         <v>236.39999389648401</v>
@@ -4566,16 +4561,16 @@
         <v>197.5</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>168</v>
+        <v>178</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>194</v>
+        <v>179</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J22" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K22" s="1">
         <v>162.1</v>
@@ -4589,16 +4584,16 @@
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.75">
       <c r="A23" s="1" t="s">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>65</v>
+        <v>74</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>99</v>
+        <v>116</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="E23" s="1">
         <v>247.69999694824199</v>
@@ -4607,16 +4602,16 @@
         <v>233.5</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J23" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K23" s="1">
         <v>170.5</v>
@@ -4630,16 +4625,16 @@
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.75">
       <c r="A24" s="1" t="s">
-        <v>91</v>
+        <v>106</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>67</v>
+        <v>77</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="E24" s="1">
         <v>263.89999389648398</v>
@@ -4648,16 +4643,16 @@
         <v>236.5</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>169</v>
+        <v>180</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>195</v>
+        <v>181</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J24" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="K24" s="1">
         <v>189.5</v>
@@ -4671,13 +4666,13 @@
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.75">
       <c r="A25" s="1" t="s">
-        <v>84</v>
+        <v>98</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>85</v>
+        <v>99</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="D25" s="1" t="s">
         <v>16</v>
@@ -4689,16 +4684,16 @@
         <v>211.5</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>171</v>
+        <v>182</v>
       </c>
       <c r="H25" s="1" t="s">
-        <v>196</v>
+        <v>183</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J25" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K25" s="1">
         <v>177.8</v>
@@ -4712,16 +4707,16 @@
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.75">
       <c r="A26" s="1" t="s">
-        <v>97</v>
+        <v>114</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>98</v>
+        <v>115</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>95</v>
+        <v>111</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="E26" s="1">
         <v>244.69999694824199</v>
@@ -4730,16 +4725,16 @@
         <v>230.5</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>172</v>
+        <v>184</v>
       </c>
       <c r="H26" s="1" t="s">
-        <v>197</v>
+        <v>185</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J26" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="K26" s="1">
         <v>170.1</v>
@@ -4753,16 +4748,16 @@
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.75">
       <c r="A27" s="1" t="s">
-        <v>103</v>
+        <v>122</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>74</v>
+        <v>86</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="E27" s="1">
         <v>210.80000305175801</v>
@@ -4771,16 +4766,16 @@
         <v>221.5</v>
       </c>
       <c r="G27" s="1" t="s">
-        <v>174</v>
+        <v>186</v>
       </c>
       <c r="H27" s="1" t="s">
-        <v>198</v>
+        <v>187</v>
       </c>
       <c r="I27" s="4" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="J27" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="K27" s="1">
         <v>136</v>
@@ -4794,16 +4789,16 @@
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.75">
       <c r="A28" s="1" t="s">
-        <v>72</v>
+        <v>84</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>73</v>
+        <v>85</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="E28" s="1">
         <v>260.89999389648398</v>
@@ -4812,16 +4807,16 @@
         <v>218.5</v>
       </c>
       <c r="G28" s="1" t="s">
-        <v>175</v>
+        <v>188</v>
       </c>
       <c r="H28" s="1" t="s">
-        <v>199</v>
+        <v>189</v>
       </c>
       <c r="I28" s="3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J28" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="K28" s="1">
         <v>184.9</v>
@@ -4835,13 +4830,13 @@
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.75">
       <c r="A29" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="D29" s="1" t="s">
         <v>16</v>
@@ -4853,16 +4848,16 @@
         <v>221.5</v>
       </c>
       <c r="G29" s="1" t="s">
-        <v>90</v>
+        <v>104</v>
       </c>
       <c r="H29" s="1" t="s">
-        <v>158</v>
+        <v>190</v>
       </c>
       <c r="I29" s="3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J29" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K29" s="1">
         <v>149.5</v>
@@ -4874,7 +4869,7 @@
         <v>302.8</v>
       </c>
       <c r="N29" s="3" t="s">
-        <v>200</v>
+        <v>191</v>
       </c>
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.75">
@@ -4891,6 +4886,7 @@
       <c r="K30" s="1"/>
       <c r="L30" s="1"/>
       <c r="M30" s="1"/>
+      <c r="N30" s="1"/>
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.75">
       <c r="A31" s="1"/>
@@ -4906,6 +4902,7 @@
       <c r="K31" s="1"/>
       <c r="L31" s="1"/>
       <c r="M31" s="1"/>
+      <c r="N31" s="1"/>
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.75">
       <c r="A32" s="1"/>
@@ -4921,8 +4918,9 @@
       <c r="K32" s="1"/>
       <c r="L32" s="1"/>
       <c r="M32" s="1"/>
-    </row>
-    <row r="33" spans="1:13" x14ac:dyDescent="0.75">
+      <c r="N32" s="1"/>
+    </row>
+    <row r="33" spans="1:14" x14ac:dyDescent="0.75">
       <c r="A33" s="1"/>
       <c r="B33" s="1"/>
       <c r="C33" s="1"/>
@@ -4936,8 +4934,9 @@
       <c r="K33" s="1"/>
       <c r="L33" s="1"/>
       <c r="M33" s="1"/>
-    </row>
-    <row r="34" spans="1:13" x14ac:dyDescent="0.75">
+      <c r="N33" s="1"/>
+    </row>
+    <row r="34" spans="1:14" x14ac:dyDescent="0.75">
       <c r="A34" s="1"/>
       <c r="B34" s="1"/>
       <c r="C34" s="1"/>
@@ -4951,8 +4950,9 @@
       <c r="K34" s="1"/>
       <c r="L34" s="1"/>
       <c r="M34" s="1"/>
-    </row>
-    <row r="35" spans="1:13" x14ac:dyDescent="0.75">
+      <c r="N34" s="1"/>
+    </row>
+    <row r="35" spans="1:14" x14ac:dyDescent="0.75">
       <c r="A35" s="1"/>
       <c r="B35" s="1"/>
       <c r="C35" s="1"/>
@@ -4966,8 +4966,9 @@
       <c r="K35" s="1"/>
       <c r="L35" s="1"/>
       <c r="M35" s="1"/>
-    </row>
-    <row r="36" spans="1:13" x14ac:dyDescent="0.75">
+      <c r="N35" s="1"/>
+    </row>
+    <row r="36" spans="1:14" x14ac:dyDescent="0.75">
       <c r="A36" s="1"/>
       <c r="B36" s="1"/>
       <c r="C36" s="1"/>
@@ -4981,8 +4982,9 @@
       <c r="K36" s="1"/>
       <c r="L36" s="1"/>
       <c r="M36" s="1"/>
-    </row>
-    <row r="37" spans="1:13" x14ac:dyDescent="0.75">
+      <c r="N36" s="1"/>
+    </row>
+    <row r="37" spans="1:14" x14ac:dyDescent="0.75">
       <c r="A37" s="1"/>
       <c r="B37" s="1"/>
       <c r="C37" s="1"/>
@@ -4996,8 +4998,9 @@
       <c r="K37" s="1"/>
       <c r="L37" s="1"/>
       <c r="M37" s="1"/>
-    </row>
-    <row r="38" spans="1:13" x14ac:dyDescent="0.75">
+      <c r="N37" s="1"/>
+    </row>
+    <row r="38" spans="1:14" x14ac:dyDescent="0.75">
       <c r="A38" s="1"/>
       <c r="B38" s="1"/>
       <c r="C38" s="1"/>
@@ -5011,8 +5014,9 @@
       <c r="K38" s="1"/>
       <c r="L38" s="1"/>
       <c r="M38" s="1"/>
-    </row>
-    <row r="39" spans="1:13" x14ac:dyDescent="0.75">
+      <c r="N38" s="1"/>
+    </row>
+    <row r="39" spans="1:14" x14ac:dyDescent="0.75">
       <c r="A39" s="1"/>
       <c r="B39" s="1"/>
       <c r="C39" s="1"/>
@@ -5026,8 +5030,9 @@
       <c r="K39" s="1"/>
       <c r="L39" s="1"/>
       <c r="M39" s="1"/>
-    </row>
-    <row r="40" spans="1:13" x14ac:dyDescent="0.75">
+      <c r="N39" s="1"/>
+    </row>
+    <row r="40" spans="1:14" x14ac:dyDescent="0.75">
       <c r="A40" s="1"/>
       <c r="B40" s="1"/>
       <c r="C40" s="1"/>
@@ -5041,8 +5046,9 @@
       <c r="K40" s="1"/>
       <c r="L40" s="1"/>
       <c r="M40" s="1"/>
-    </row>
-    <row r="41" spans="1:13" x14ac:dyDescent="0.75">
+      <c r="N40" s="1"/>
+    </row>
+    <row r="41" spans="1:14" x14ac:dyDescent="0.75">
       <c r="A41" s="1"/>
       <c r="B41" s="1"/>
       <c r="C41" s="1"/>
@@ -5056,8 +5062,9 @@
       <c r="K41" s="1"/>
       <c r="L41" s="1"/>
       <c r="M41" s="1"/>
-    </row>
-    <row r="42" spans="1:13" x14ac:dyDescent="0.75">
+      <c r="N41" s="1"/>
+    </row>
+    <row r="42" spans="1:14" x14ac:dyDescent="0.75">
       <c r="A42" s="1"/>
       <c r="B42" s="1"/>
       <c r="C42" s="1"/>
@@ -5071,8 +5078,9 @@
       <c r="K42" s="1"/>
       <c r="L42" s="1"/>
       <c r="M42" s="1"/>
-    </row>
-    <row r="43" spans="1:13" x14ac:dyDescent="0.75">
+      <c r="N42" s="1"/>
+    </row>
+    <row r="43" spans="1:14" x14ac:dyDescent="0.75">
       <c r="A43" s="1"/>
       <c r="B43" s="1"/>
       <c r="C43" s="1"/>
@@ -5086,8 +5094,9 @@
       <c r="K43" s="1"/>
       <c r="L43" s="1"/>
       <c r="M43" s="1"/>
-    </row>
-    <row r="44" spans="1:13" x14ac:dyDescent="0.75">
+      <c r="N43" s="1"/>
+    </row>
+    <row r="44" spans="1:14" x14ac:dyDescent="0.75">
       <c r="A44" s="1"/>
       <c r="B44" s="1"/>
       <c r="C44" s="1"/>
@@ -5101,8 +5110,9 @@
       <c r="K44" s="1"/>
       <c r="L44" s="1"/>
       <c r="M44" s="1"/>
-    </row>
-    <row r="45" spans="1:13" x14ac:dyDescent="0.75">
+      <c r="N44" s="1"/>
+    </row>
+    <row r="45" spans="1:14" x14ac:dyDescent="0.75">
       <c r="A45" s="1"/>
       <c r="B45" s="1"/>
       <c r="C45" s="1"/>
@@ -5117,7 +5127,7 @@
       <c r="L45" s="1"/>
       <c r="M45" s="1"/>
     </row>
-    <row r="46" spans="1:13" x14ac:dyDescent="0.75">
+    <row r="46" spans="1:14" x14ac:dyDescent="0.75">
       <c r="A46" s="1"/>
       <c r="B46" s="1"/>
       <c r="C46" s="1"/>
@@ -5132,7 +5142,7 @@
       <c r="L46" s="1"/>
       <c r="M46" s="1"/>
     </row>
-    <row r="47" spans="1:13" x14ac:dyDescent="0.75">
+    <row r="47" spans="1:14" x14ac:dyDescent="0.75">
       <c r="A47" s="1"/>
       <c r="B47" s="1"/>
       <c r="C47" s="1"/>
@@ -5147,7 +5157,7 @@
       <c r="L47" s="1"/>
       <c r="M47" s="1"/>
     </row>
-    <row r="48" spans="1:13" x14ac:dyDescent="0.75">
+    <row r="48" spans="1:14" x14ac:dyDescent="0.75">
       <c r="A48" s="1"/>
       <c r="B48" s="1"/>
       <c r="C48" s="1"/>
@@ -5642,7 +5652,7 @@
       <c r="L80" s="1"/>
       <c r="M80" s="1"/>
     </row>
-    <row r="81" spans="1:14" x14ac:dyDescent="0.75">
+    <row r="81" spans="1:13" x14ac:dyDescent="0.75">
       <c r="A81" s="1"/>
       <c r="B81" s="1"/>
       <c r="C81" s="1"/>
@@ -5657,7 +5667,7 @@
       <c r="L81" s="1"/>
       <c r="M81" s="1"/>
     </row>
-    <row r="82" spans="1:14" x14ac:dyDescent="0.75">
+    <row r="82" spans="1:13" x14ac:dyDescent="0.75">
       <c r="A82" s="1"/>
       <c r="B82" s="1"/>
       <c r="C82" s="1"/>
@@ -5672,7 +5682,7 @@
       <c r="L82" s="1"/>
       <c r="M82" s="1"/>
     </row>
-    <row r="83" spans="1:14" x14ac:dyDescent="0.75">
+    <row r="83" spans="1:13" x14ac:dyDescent="0.75">
       <c r="A83" s="1"/>
       <c r="B83" s="1"/>
       <c r="C83" s="1"/>
@@ -5687,7 +5697,7 @@
       <c r="L83" s="1"/>
       <c r="M83" s="1"/>
     </row>
-    <row r="84" spans="1:14" x14ac:dyDescent="0.75">
+    <row r="84" spans="1:13" x14ac:dyDescent="0.75">
       <c r="A84" s="1"/>
       <c r="B84" s="1"/>
       <c r="C84" s="1"/>
@@ -5702,7 +5712,7 @@
       <c r="L84" s="1"/>
       <c r="M84" s="1"/>
     </row>
-    <row r="85" spans="1:14" x14ac:dyDescent="0.75">
+    <row r="85" spans="1:13" x14ac:dyDescent="0.75">
       <c r="A85" s="1"/>
       <c r="B85" s="1"/>
       <c r="C85" s="1"/>
@@ -5716,11 +5726,6 @@
       <c r="K85" s="1"/>
       <c r="L85" s="1"/>
       <c r="M85" s="1"/>
-    </row>
-    <row r="89" spans="1:14" x14ac:dyDescent="0.75">
-      <c r="N89" t="s">
-        <v>283</v>
-      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5817,16 +5822,16 @@
     </row>
     <row r="2" spans="1:40" x14ac:dyDescent="0.75">
       <c r="A2" s="1" t="s">
-        <v>93</v>
+        <v>109</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>94</v>
+        <v>110</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="E2" s="1">
         <v>228.69999694824199</v>
@@ -5835,16 +5840,16 @@
         <v>235.5</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>201</v>
+        <v>192</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>217</v>
+        <v>193</v>
       </c>
       <c r="I2" s="4" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K2" s="1">
         <v>152.1</v>
@@ -5858,13 +5863,13 @@
     </row>
     <row r="3" spans="1:40" x14ac:dyDescent="0.75">
       <c r="A3" s="1" t="s">
-        <v>91</v>
+        <v>106</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>94</v>
+        <v>110</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>16</v>
@@ -5876,16 +5881,16 @@
         <v>238.5</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>202</v>
+        <v>194</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>204</v>
+        <v>195</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="K3" s="1">
         <v>165.8</v>
@@ -5899,13 +5904,13 @@
     </row>
     <row r="4" spans="1:40" x14ac:dyDescent="0.75">
       <c r="A4" s="1" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>16</v>
@@ -5917,16 +5922,16 @@
         <v>222.5</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>203</v>
+        <v>196</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>231</v>
+        <v>197</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="K4" s="1">
         <v>152.9</v>
@@ -5940,16 +5945,16 @@
     </row>
     <row r="5" spans="1:40" x14ac:dyDescent="0.75">
       <c r="A5" s="1" t="s">
-        <v>59</v>
+        <v>67</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="E5" s="1">
         <v>211.39999389648401</v>
@@ -5958,16 +5963,16 @@
         <v>230.5</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>205</v>
+        <v>198</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>232</v>
+        <v>199</v>
       </c>
       <c r="I5" s="4" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K5" s="1">
         <v>134.80000000000001</v>
@@ -5981,13 +5986,13 @@
     </row>
     <row r="6" spans="1:40" x14ac:dyDescent="0.75">
       <c r="A6" s="1" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>65</v>
+        <v>74</v>
       </c>
       <c r="D6" s="1" t="s">
         <v>16</v>
@@ -5999,16 +6004,16 @@
         <v>190.5</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>206</v>
+        <v>200</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>233</v>
+        <v>201</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J6" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K6" s="1">
         <v>138.5</v>
@@ -6022,16 +6027,16 @@
     </row>
     <row r="7" spans="1:40" x14ac:dyDescent="0.75">
       <c r="A7" s="1" t="s">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>65</v>
+        <v>74</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="E7" s="1">
         <v>252.10000610351599</v>
@@ -6040,16 +6045,16 @@
         <v>224.5</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>208</v>
+        <v>202</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>54</v>
+        <v>203</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J7" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="K7" s="1">
         <v>174.8</v>
@@ -6063,16 +6068,16 @@
     </row>
     <row r="8" spans="1:40" x14ac:dyDescent="0.75">
       <c r="A8" s="1" t="s">
-        <v>63</v>
+        <v>72</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>64</v>
+        <v>73</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="E8" s="1">
         <v>216.89999389648401</v>
@@ -6081,16 +6086,16 @@
         <v>229.5</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>234</v>
+        <v>205</v>
       </c>
       <c r="I8" s="4" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="J8" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K8" s="1">
         <v>140.69999999999999</v>
@@ -6104,13 +6109,13 @@
     </row>
     <row r="9" spans="1:40" x14ac:dyDescent="0.75">
       <c r="A9" s="1" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>64</v>
+        <v>73</v>
       </c>
       <c r="D9" s="1" t="s">
         <v>16</v>
@@ -6122,16 +6127,16 @@
         <v>232.5</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>235</v>
+        <v>207</v>
       </c>
       <c r="I9" s="4" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="J9" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K9" s="1">
         <v>138.30000000000001</v>
@@ -6145,16 +6150,16 @@
     </row>
     <row r="10" spans="1:40" x14ac:dyDescent="0.75">
       <c r="A10" s="1" t="s">
-        <v>111</v>
+        <v>131</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="E10" s="1">
         <v>253</v>
@@ -6163,16 +6168,16 @@
         <v>264.5</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>221</v>
+        <v>209</v>
       </c>
       <c r="I10" s="4" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="J10" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K10" s="1">
         <v>175.4</v>
@@ -6186,13 +6191,13 @@
     </row>
     <row r="11" spans="1:40" x14ac:dyDescent="0.75">
       <c r="A11" s="1" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="D11" s="1" t="s">
         <v>16</v>
@@ -6204,16 +6209,16 @@
         <v>236.5</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>236</v>
+        <v>210</v>
       </c>
       <c r="I11" s="4" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="J11" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="K11" s="1">
         <v>132.1</v>
@@ -6227,16 +6232,16 @@
     </row>
     <row r="12" spans="1:40" x14ac:dyDescent="0.75">
       <c r="A12" s="1" t="s">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>74</v>
+        <v>86</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="E12" s="1">
         <v>238.30000305175801</v>
@@ -6245,16 +6250,16 @@
         <v>232.5</v>
       </c>
       <c r="G12" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="H12" s="1" t="s">
         <v>212</v>
       </c>
-      <c r="H12" s="1" t="s">
-        <v>119</v>
-      </c>
       <c r="I12" s="3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J12" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="K12" s="1">
         <v>162.80000000000001</v>
@@ -6268,13 +6273,13 @@
     </row>
     <row r="13" spans="1:40" x14ac:dyDescent="0.75">
       <c r="A13" s="1" t="s">
-        <v>103</v>
+        <v>122</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>74</v>
+        <v>86</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="D13" s="1" t="s">
         <v>16</v>
@@ -6289,13 +6294,13 @@
         <v>213</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>237</v>
+        <v>214</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J13" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="K13" s="1">
         <v>161.9</v>
@@ -6309,13 +6314,13 @@
     </row>
     <row r="14" spans="1:40" x14ac:dyDescent="0.75">
       <c r="A14" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="D14" s="1" t="s">
         <v>16</v>
@@ -6327,16 +6332,16 @@
         <v>215.5</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>238</v>
+        <v>216</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J14" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K14" s="1">
         <v>159.30000000000001</v>
@@ -6350,16 +6355,16 @@
     </row>
     <row r="15" spans="1:40" x14ac:dyDescent="0.75">
       <c r="A15" s="1" t="s">
-        <v>89</v>
+        <v>103</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="E15" s="1">
         <v>275.89999389648398</v>
@@ -6368,16 +6373,16 @@
         <v>267.5</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>239</v>
+        <v>218</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J15" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="K15" s="1">
         <v>198.8</v>
@@ -6391,16 +6396,16 @@
     </row>
     <row r="16" spans="1:40" x14ac:dyDescent="0.75">
       <c r="A16" s="1" t="s">
-        <v>114</v>
+        <v>136</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>68</v>
+        <v>78</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="E16" s="1">
         <v>209.60000610351599</v>
@@ -6409,16 +6414,16 @@
         <v>224.5</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>240</v>
+        <v>220</v>
       </c>
       <c r="I16" s="4" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="J16" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K16" s="1">
         <v>132.5</v>
@@ -6432,13 +6437,13 @@
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.75">
       <c r="A17" s="1" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>68</v>
+        <v>78</v>
       </c>
       <c r="D17" s="1" t="s">
         <v>16</v>
@@ -6450,16 +6455,16 @@
         <v>222.5</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>241</v>
+        <v>222</v>
       </c>
       <c r="I17" s="4" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="J17" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="K17" s="1">
         <v>114.4</v>
@@ -6473,16 +6478,16 @@
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.75">
       <c r="A18" s="1" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>67</v>
+        <v>77</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="E18" s="1">
         <v>195.19999694824199</v>
@@ -6491,16 +6496,16 @@
         <v>197.5</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>242</v>
+        <v>225</v>
       </c>
       <c r="I18" s="4" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="J18" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K18" s="1">
         <v>117.9</v>
@@ -6514,13 +6519,13 @@
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.75">
       <c r="A19" s="1" t="s">
-        <v>101</v>
+        <v>119</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>67</v>
+        <v>77</v>
       </c>
       <c r="D19" s="1" t="s">
         <v>16</v>
@@ -6532,16 +6537,16 @@
         <v>239.5</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>75</v>
+        <v>87</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>118</v>
+        <v>226</v>
       </c>
       <c r="I19" s="4" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="J19" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K19" s="1">
         <v>154.80000000000001</v>
@@ -6555,13 +6560,13 @@
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.75">
       <c r="A20" s="1" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>98</v>
+        <v>115</v>
       </c>
       <c r="D20" s="1" t="s">
         <v>16</v>
@@ -6573,16 +6578,16 @@
         <v>253.5</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>222</v>
+        <v>227</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>243</v>
+        <v>228</v>
       </c>
       <c r="I20" s="4" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="J20" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="K20" s="1">
         <v>173.9</v>
@@ -6596,16 +6601,16 @@
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.75">
       <c r="A21" s="1" t="s">
-        <v>97</v>
+        <v>114</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>98</v>
+        <v>115</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="E21" s="1">
         <v>238.10000610351599</v>
@@ -6614,16 +6619,16 @@
         <v>217.5</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>244</v>
+        <v>230</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J21" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="K21" s="1">
         <v>162.6</v>
@@ -6643,7 +6648,7 @@
         <v>14</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>86</v>
+        <v>100</v>
       </c>
       <c r="D22" s="1" t="s">
         <v>16</v>
@@ -6655,16 +6660,16 @@
         <v>215.5</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>188</v>
+        <v>166</v>
       </c>
       <c r="I22" s="4" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="J22" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="K22" s="1">
         <v>134</v>
@@ -6678,16 +6683,16 @@
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.75">
       <c r="A23" s="1" t="s">
-        <v>108</v>
+        <v>128</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>86</v>
+        <v>100</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="E23" s="1">
         <v>212.30000305175801</v>
@@ -6696,16 +6701,16 @@
         <v>202.5</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>170</v>
+        <v>231</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J23" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K23" s="1">
         <v>135.1</v>
@@ -6719,16 +6724,16 @@
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.75">
       <c r="A24" s="1" t="s">
-        <v>84</v>
+        <v>98</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>85</v>
+        <v>99</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="E24" s="1">
         <v>250.19999694824199</v>
@@ -6737,16 +6742,16 @@
         <v>217.5</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>224</v>
+        <v>232</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>207</v>
+        <v>233</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J24" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="K24" s="1">
         <v>173.2</v>
@@ -6760,13 +6765,13 @@
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.75">
       <c r="A25" s="1" t="s">
-        <v>167</v>
+        <v>177</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>15</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>85</v>
+        <v>99</v>
       </c>
       <c r="D25" s="1" t="s">
         <v>16</v>
@@ -6778,16 +6783,16 @@
         <v>211.5</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H25" s="1" t="s">
-        <v>245</v>
+        <v>235</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J25" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K25" s="1">
         <v>167.3</v>
@@ -6801,16 +6806,16 @@
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.75">
       <c r="A26" s="1" t="s">
-        <v>226</v>
+        <v>236</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="E26" s="1">
         <v>233.69999694824199</v>
@@ -6819,16 +6824,16 @@
         <v>235.5</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>227</v>
+        <v>237</v>
       </c>
       <c r="H26" s="1" t="s">
-        <v>173</v>
+        <v>238</v>
       </c>
       <c r="I26" s="4" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="J26" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K26" s="1">
         <v>158.6</v>
@@ -6842,13 +6847,13 @@
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.75">
       <c r="A27" s="1" t="s">
-        <v>228</v>
+        <v>239</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="D27" s="1" t="s">
         <v>16</v>
@@ -6860,16 +6865,16 @@
         <v>200.5</v>
       </c>
       <c r="G27" s="1" t="s">
-        <v>229</v>
+        <v>240</v>
       </c>
       <c r="H27" s="1" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="I27" s="3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J27" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="K27" s="1">
         <v>124.2</v>
@@ -6881,7 +6886,7 @@
         <v>276.89999999999998</v>
       </c>
       <c r="N27" s="1" t="s">
-        <v>230</v>
+        <v>242</v>
       </c>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.75">
@@ -35554,10 +35559,10 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.75">
       <c r="A2" s="1" t="s">
-        <v>84</v>
+        <v>98</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>85</v>
+        <v>99</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>14</v>
@@ -35575,13 +35580,13 @@
         <v>200</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>252</v>
+        <v>243</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="K2" s="1">
         <v>158.69999999999999</v>
@@ -35601,10 +35606,10 @@
         <v>14</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>85</v>
+        <v>99</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="E3" s="1">
         <v>227.69999694824199</v>
@@ -35616,13 +35621,13 @@
         <v>242</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>253</v>
+        <v>244</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K3" s="1">
         <v>152.4</v>
@@ -35636,16 +35641,16 @@
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.75">
       <c r="A4" s="1" t="s">
-        <v>114</v>
+        <v>136</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>68</v>
+        <v>78</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="E4" s="1">
         <v>222.5</v>
@@ -35657,13 +35662,13 @@
         <v>200</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>254</v>
+        <v>245</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="K4" s="1">
         <v>147.69999999999999</v>
@@ -35677,16 +35682,16 @@
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.75">
       <c r="A5" s="1" t="s">
-        <v>228</v>
+        <v>239</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>68</v>
+        <v>78</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="E5" s="1">
         <v>214.80000305175801</v>
@@ -35698,13 +35703,13 @@
         <v>350</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>255</v>
+        <v>246</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K5" s="1">
         <v>138.80000000000001</v>
@@ -35718,13 +35723,13 @@
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.75">
       <c r="A6" s="1" t="s">
-        <v>101</v>
+        <v>119</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="D6" s="1" t="s">
         <v>16</v>
@@ -35739,13 +35744,13 @@
         <v>289</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>256</v>
+        <v>247</v>
       </c>
       <c r="I6" s="4" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="J6" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="K6" s="1">
         <v>150.30000000000001</v>
@@ -35759,16 +35764,16 @@
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.75">
       <c r="A7" s="1" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="E7" s="1">
         <v>219.89999389648401</v>
@@ -35780,13 +35785,13 @@
         <v>130</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>257</v>
+        <v>248</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J7" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="K7" s="1">
         <v>144.4</v>
@@ -35800,13 +35805,13 @@
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.75">
       <c r="A8" s="1" t="s">
-        <v>89</v>
+        <v>103</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="D8" s="1" t="s">
         <v>16</v>
@@ -35821,13 +35826,13 @@
         <v>168</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>258</v>
+        <v>249</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J8" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="K8" s="1">
         <v>188.3</v>
@@ -35841,16 +35846,16 @@
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.75">
       <c r="A9" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="D9" s="1" t="s">
         <v>31</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>29</v>
       </c>
       <c r="E9" s="1">
         <v>221.80000305175801</v>
@@ -35862,13 +35867,13 @@
         <v>184</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>259</v>
+        <v>250</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J9" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="K9" s="1">
         <v>147.4</v>
@@ -35882,13 +35887,13 @@
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.75">
       <c r="A10" s="1" t="s">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>16</v>
@@ -35903,13 +35908,13 @@
         <v>270</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>260</v>
+        <v>251</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J10" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K10" s="1">
         <v>163.6</v>
@@ -35923,16 +35928,16 @@
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.75">
       <c r="A11" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="E11" s="1">
         <v>244.89999389648401</v>
@@ -35944,13 +35949,13 @@
         <v>147</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J11" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="K11" s="1">
         <v>170.8</v>
@@ -35964,13 +35969,13 @@
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.75">
       <c r="A12" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="C12" s="1" t="s">
         <v>40</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>37</v>
       </c>
       <c r="D12" s="1" t="s">
         <v>16</v>
@@ -35985,13 +35990,13 @@
         <v>117</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>184</v>
+        <v>157</v>
       </c>
       <c r="I12" s="4" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="J12" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K12" s="1">
         <v>169.8</v>
@@ -36005,16 +36010,16 @@
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.75">
       <c r="A13" s="1" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="E13" s="1">
         <v>235</v>
@@ -36026,13 +36031,13 @@
         <v>212</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>259</v>
+        <v>250</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J13" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="K13" s="1">
         <v>160.4</v>
@@ -36046,13 +36051,13 @@
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.75">
       <c r="A14" s="1" t="s">
-        <v>111</v>
+        <v>131</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="D14" s="1" t="s">
         <v>16</v>
@@ -36067,13 +36072,13 @@
         <v>319</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>248</v>
+        <v>253</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J14" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K14" s="1">
         <v>177.3</v>
@@ -36087,16 +36092,16 @@
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.75">
       <c r="A15" s="1" t="s">
-        <v>59</v>
+        <v>67</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="E15" s="1">
         <v>230.89999389648401</v>
@@ -36108,13 +36113,13 @@
         <v>337</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>35</v>
+        <v>254</v>
       </c>
       <c r="I15" s="4" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="J15" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="K15" s="1">
         <v>153.6</v>
@@ -36128,16 +36133,16 @@
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.75">
       <c r="A16" s="1" t="s">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="B16" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="C16" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="C16" s="1" t="s">
-        <v>42</v>
-      </c>
       <c r="D16" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="E16" s="1">
         <v>241.80000305175801</v>
@@ -36149,13 +36154,13 @@
         <v>150</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>261</v>
+        <v>255</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J16" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="K16" s="1">
         <v>165.5</v>
@@ -36169,13 +36174,13 @@
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.75">
       <c r="A17" s="1" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="D17" s="1" t="s">
         <v>16</v>
@@ -36190,13 +36195,13 @@
         <v>203</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>247</v>
+        <v>256</v>
       </c>
       <c r="I17" s="4" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="J17" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K17" s="1">
         <v>133.5</v>
@@ -36210,13 +36215,13 @@
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.75">
       <c r="A18" s="1" t="s">
-        <v>97</v>
+        <v>114</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>98</v>
+        <v>115</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="D18" s="1" t="s">
         <v>16</v>
@@ -36231,13 +36236,13 @@
         <v>326</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>262</v>
+        <v>257</v>
       </c>
       <c r="I18" s="4" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="J18" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="K18" s="1">
         <v>144.4</v>
@@ -36251,13 +36256,13 @@
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.75">
       <c r="A19" s="1" t="s">
-        <v>91</v>
+        <v>106</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>86</v>
+        <v>100</v>
       </c>
       <c r="D19" s="1" t="s">
         <v>16</v>
@@ -36272,13 +36277,13 @@
         <v>209</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>263</v>
+        <v>258</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J19" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="K19" s="1">
         <v>177.6</v>
@@ -36292,16 +36297,16 @@
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.75">
       <c r="A20" s="1" t="s">
-        <v>108</v>
+        <v>128</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>86</v>
+        <v>100</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="E20" s="1">
         <v>220.60000610351599</v>
@@ -36313,13 +36318,13 @@
         <v>126</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J20" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="K20" s="1">
         <v>144.30000000000001</v>
@@ -36333,13 +36338,13 @@
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.75">
       <c r="A21" s="1" t="s">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>65</v>
+        <v>74</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>95</v>
+        <v>111</v>
       </c>
       <c r="D21" s="1" t="s">
         <v>16</v>
@@ -36354,13 +36359,13 @@
         <v>375</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>264</v>
+        <v>259</v>
       </c>
       <c r="I21" s="4" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="J21" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="K21" s="1">
         <v>166.5</v>
@@ -36374,16 +36379,16 @@
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.75">
       <c r="A22" s="1" t="s">
-        <v>112</v>
+        <v>133</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>95</v>
+        <v>111</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>65</v>
+        <v>74</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="E22" s="1">
         <v>237.39999389648401</v>
@@ -36395,13 +36400,13 @@
         <v>262</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>79</v>
+        <v>260</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J22" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K22" s="1">
         <v>163</v>
@@ -36797,10 +36802,10 @@
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.75">
       <c r="A2" s="1" t="s">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>65</v>
+        <v>74</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>15</v>
@@ -36818,13 +36823,13 @@
         <v>389</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K2" s="1">
         <v>174</v>
@@ -36838,13 +36843,13 @@
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.75">
       <c r="A3" s="1" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>73</v>
+        <v>85</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>16</v>
@@ -36859,13 +36864,13 @@
         <v>166</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="I3" s="4" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K3" s="1">
         <v>182.4</v>
@@ -36879,16 +36884,16 @@
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.75">
       <c r="A4" s="1" t="s">
-        <v>72</v>
+        <v>84</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>73</v>
+        <v>85</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="E4" s="1">
         <v>245.80000305175801</v>
@@ -36900,13 +36905,13 @@
         <v>231</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K4" s="1">
         <v>169.8</v>
@@ -36920,16 +36925,16 @@
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.75">
       <c r="A5" s="1" t="s">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="E5" s="1">
         <v>246.80000305175801</v>
@@ -36941,13 +36946,13 @@
         <v>318</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>188</v>
+        <v>166</v>
       </c>
       <c r="I5" s="4" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="K5" s="1">
         <v>170.7</v>
@@ -36961,13 +36966,13 @@
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.75">
       <c r="A6" s="1" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="D6" s="1" t="s">
         <v>16</v>
@@ -36982,13 +36987,13 @@
         <v>221</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>268</v>
+        <v>264</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J6" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K6" s="1">
         <v>156.69999999999999</v>
@@ -37002,16 +37007,16 @@
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.75">
       <c r="A7" s="1" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>95</v>
+        <v>111</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="E7" s="1">
         <v>235</v>
@@ -37023,13 +37028,13 @@
         <v>228</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
       <c r="I7" s="4" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="J7" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K7" s="1">
         <v>158.80000000000001</v>
@@ -37043,13 +37048,13 @@
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.75">
       <c r="A8" s="1" t="s">
-        <v>112</v>
+        <v>133</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>95</v>
+        <v>111</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="D8" s="1" t="s">
         <v>16</v>
@@ -37064,13 +37069,13 @@
         <v>212</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J8" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="K8" s="1">
         <v>173.5</v>
@@ -37084,16 +37089,16 @@
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.75">
       <c r="A9" s="1" t="s">
-        <v>97</v>
+        <v>114</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>98</v>
+        <v>115</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="E9" s="1">
         <v>233.60000610351599</v>
@@ -37105,13 +37110,13 @@
         <v>242</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>249</v>
+        <v>267</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J9" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K9" s="1">
         <v>158.4</v>
@@ -37125,13 +37130,13 @@
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.75">
       <c r="A10" s="1" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>98</v>
+        <v>115</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>16</v>
@@ -37146,13 +37151,13 @@
         <v>280</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>88</v>
+        <v>268</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J10" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K10" s="1">
         <v>142.1</v>
@@ -37166,13 +37171,13 @@
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.75">
       <c r="A11" s="1" t="s">
-        <v>108</v>
+        <v>128</v>
       </c>
       <c r="B11" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="C11" s="1" t="s">
         <v>86</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>74</v>
       </c>
       <c r="D11" s="1" t="s">
         <v>16</v>
@@ -37187,13 +37192,13 @@
         <v>225</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J11" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K11" s="1">
         <v>139.4</v>
@@ -37207,16 +37212,16 @@
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.75">
       <c r="A12" s="1" t="s">
-        <v>111</v>
+        <v>131</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>67</v>
+        <v>77</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="E12" s="1">
         <v>264.29998779296898</v>
@@ -37228,13 +37233,13 @@
         <v>237</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>238</v>
+        <v>216</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J12" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="K12" s="1">
         <v>188.1</v>
@@ -37248,13 +37253,13 @@
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.75">
       <c r="A13" s="1" t="s">
-        <v>66</v>
+        <v>76</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>67</v>
+        <v>77</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="D13" s="1" t="s">
         <v>16</v>
@@ -37269,13 +37274,13 @@
         <v>283</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J13" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K13" s="1">
         <v>114.6</v>
@@ -37289,16 +37294,16 @@
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.75">
       <c r="A14" s="1" t="s">
-        <v>63</v>
+        <v>72</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>64</v>
+        <v>73</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="E14" s="1">
         <v>228.30000305175801</v>
@@ -37310,13 +37315,13 @@
         <v>244</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>179</v>
+        <v>271</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J14" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K14" s="1">
         <v>152.9</v>
@@ -37330,13 +37335,13 @@
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.75">
       <c r="A15" s="1" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>64</v>
+        <v>73</v>
       </c>
       <c r="D15" s="1" t="s">
         <v>16</v>
@@ -37351,13 +37356,13 @@
         <v>179</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>250</v>
+        <v>273</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J15" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K15" s="1">
         <v>133.80000000000001</v>
@@ -37371,16 +37376,16 @@
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.75">
       <c r="A16" s="1" t="s">
-        <v>93</v>
+        <v>109</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>94</v>
+        <v>110</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="E16" s="1">
         <v>219.39999389648401</v>
@@ -37395,10 +37400,10 @@
         <v>274</v>
       </c>
       <c r="I16" s="4" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="J16" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="K16" s="1">
         <v>141.6</v>
@@ -37412,13 +37417,13 @@
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.75">
       <c r="A17" s="1" t="s">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>94</v>
+        <v>110</v>
       </c>
       <c r="D17" s="1" t="s">
         <v>16</v>
@@ -37433,13 +37438,13 @@
         <v>198</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>177</v>
+        <v>141</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J17" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="K17" s="1">
         <v>141.1</v>
@@ -37453,13 +37458,13 @@
     </row>
     <row r="18" spans="1:13" x14ac:dyDescent="0.75">
       <c r="A18" s="1" t="s">
-        <v>84</v>
+        <v>98</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>85</v>
+        <v>99</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>99</v>
+        <v>116</v>
       </c>
       <c r="D18" s="1" t="s">
         <v>16</v>
@@ -37474,13 +37479,13 @@
         <v>220</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>178</v>
+        <v>145</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J18" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="K18" s="1">
         <v>158.5</v>
@@ -37494,16 +37499,16 @@
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.75">
       <c r="A19" s="1" t="s">
-        <v>101</v>
+        <v>119</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="E19" s="1">
         <v>232</v>
@@ -37515,13 +37520,13 @@
         <v>379</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>231</v>
+        <v>197</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J19" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K19" s="1">
         <v>156.4</v>
@@ -37541,7 +37546,7 @@
         <v>14</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D20" s="1" t="s">
         <v>16</v>
@@ -37559,10 +37564,10 @@
         <v>275</v>
       </c>
       <c r="I20" s="4" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="J20" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="K20" s="1">
         <v>145.9</v>
@@ -37576,16 +37581,16 @@
     </row>
     <row r="21" spans="1:13" x14ac:dyDescent="0.75">
       <c r="A21" s="1" t="s">
-        <v>89</v>
+        <v>103</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="E21" s="1">
         <v>250.39999389648401</v>
@@ -37600,10 +37605,10 @@
         <v>276</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J21" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K21" s="1">
         <v>173.3</v>
@@ -37617,13 +37622,13 @@
     </row>
     <row r="22" spans="1:13" x14ac:dyDescent="0.75">
       <c r="A22" s="1" t="s">
-        <v>226</v>
+        <v>236</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="D22" s="1" t="s">
         <v>16</v>
@@ -37638,13 +37643,13 @@
         <v>251</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>247</v>
+        <v>256</v>
       </c>
       <c r="I22" s="4" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="J22" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="K22" s="1">
         <v>135.30000000000001</v>
@@ -37658,16 +37663,16 @@
     </row>
     <row r="23" spans="1:13" x14ac:dyDescent="0.75">
       <c r="A23" s="1" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="E23" s="1">
         <v>239.10000610351599</v>
@@ -37679,13 +37684,13 @@
         <v>273</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>124</v>
+        <v>38</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J23" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K23" s="1">
         <v>161.69999999999999</v>
@@ -37699,13 +37704,13 @@
     </row>
     <row r="24" spans="1:13" x14ac:dyDescent="0.75">
       <c r="A24" s="1" t="s">
-        <v>91</v>
+        <v>106</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="D24" s="1" t="s">
         <v>16</v>
@@ -37723,10 +37728,10 @@
         <v>277</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J24" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K24" s="1">
         <v>176.5</v>
@@ -37740,16 +37745,16 @@
     </row>
     <row r="25" spans="1:13" x14ac:dyDescent="0.75">
       <c r="A25" s="1" t="s">
-        <v>228</v>
+        <v>239</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="E25" s="1">
         <v>208.69999694824199</v>
@@ -37764,10 +37769,10 @@
         <v>278</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J25" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K25" s="1">
         <v>132.4</v>
@@ -37789,7 +37794,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:M25"/>
-  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
+  <sheetFormatPr defaultColWidth="10.90625" defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="2" width="6" customWidth="1"/>
@@ -37800,938 +37805,1187 @@
     <col min="7" max="7" width="8" customWidth="1"/>
     <col min="8" max="8" width="11" customWidth="1"/>
     <col min="9" max="9" width="8.2265625" customWidth="1"/>
-    <col min="10" max="10" width="5" customWidth="1"/>
+    <col min="10" max="10" width="9.04296875" customWidth="1"/>
     <col min="11" max="13" width="7" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.75">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="8" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="8" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="8" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="8" t="s">
+      <c r="E1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" ht="16.75" customHeight="1" x14ac:dyDescent="0.75">
+      <c r="A2" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="B2" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="C2" s="10" t="s">
+        <v>116</v>
+      </c>
+      <c r="D2" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="E2" s="11">
+        <v>218.3999939</v>
+      </c>
+      <c r="F2" s="11">
+        <v>228.5</v>
+      </c>
+      <c r="G2" s="10">
+        <v>174</v>
+      </c>
+      <c r="H2" s="12">
+        <v>0.437</v>
+      </c>
+      <c r="I2" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="J2" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="K2" s="11">
+        <v>142.1</v>
+      </c>
+      <c r="L2" s="11">
+        <v>218.6</v>
+      </c>
+      <c r="M2" s="11">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.75">
+      <c r="A3" s="10" t="s">
+        <v>62</v>
+      </c>
+      <c r="B3" s="10" t="s">
+        <v>63</v>
+      </c>
+      <c r="C3" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="D3" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="E3" s="11">
+        <v>233.6000061</v>
+      </c>
+      <c r="F3" s="11">
+        <v>196.5</v>
+      </c>
+      <c r="G3" s="10">
+        <v>283</v>
+      </c>
+      <c r="H3" s="12">
+        <v>0.73399999999999999</v>
+      </c>
+      <c r="I3" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="J3" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="K3" s="11">
+        <v>156.9</v>
+      </c>
+      <c r="L3" s="11">
+        <v>233.5</v>
+      </c>
+      <c r="M3" s="11">
+        <v>308.3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.75">
+      <c r="A4" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="B4" s="10" t="s">
+        <v>115</v>
+      </c>
+      <c r="C4" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="D4" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="E4" s="11">
+        <v>237.8999939</v>
+      </c>
+      <c r="F4" s="11">
+        <v>223.5</v>
+      </c>
+      <c r="G4" s="10">
+        <v>174</v>
+      </c>
+      <c r="H4" s="12">
+        <v>0.59199999999999997</v>
+      </c>
+      <c r="I4" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="J4" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="K4" s="11">
+        <v>162</v>
+      </c>
+      <c r="L4" s="11">
+        <v>237.2</v>
+      </c>
+      <c r="M4" s="11">
+        <v>313.7</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.75">
+      <c r="A5" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="B5" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="C5" s="10" t="s">
+        <v>115</v>
+      </c>
+      <c r="D5" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="E5" s="11">
+        <v>215.6000061</v>
+      </c>
+      <c r="F5" s="11">
+        <v>197.5</v>
+      </c>
+      <c r="G5" s="10">
+        <v>45</v>
+      </c>
+      <c r="H5" s="12">
+        <v>0.61399999999999999</v>
+      </c>
+      <c r="I5" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="J5" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="K5" s="11">
+        <v>140.1</v>
+      </c>
+      <c r="L5" s="11">
+        <v>215.8</v>
+      </c>
+      <c r="M5" s="11">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.75">
+      <c r="A6" s="10" t="s">
+        <v>136</v>
+      </c>
+      <c r="B6" s="10" t="s">
+        <v>78</v>
+      </c>
+      <c r="C6" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="D6" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="E6" s="11">
+        <v>216.5</v>
+      </c>
+      <c r="F6" s="11">
+        <v>206.5</v>
+      </c>
+      <c r="G6" s="10">
+        <v>235</v>
+      </c>
+      <c r="H6" s="12">
+        <v>0.56599999999999995</v>
+      </c>
+      <c r="I6" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="J6" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="K6" s="11">
+        <v>139.19999999999999</v>
+      </c>
+      <c r="L6" s="11">
+        <v>216.9</v>
+      </c>
+      <c r="M6" s="11">
+        <v>290.89999999999998</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.75">
+      <c r="A7" s="10" t="s">
+        <v>92</v>
+      </c>
+      <c r="B7" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="C7" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="D7" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="E7" s="11">
+        <v>267.2000122</v>
+      </c>
+      <c r="F7" s="11">
+        <v>262.5</v>
+      </c>
+      <c r="G7" s="10">
+        <v>181</v>
+      </c>
+      <c r="H7" s="12">
+        <v>0.54500000000000004</v>
+      </c>
+      <c r="I7" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="J7" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="K7" s="11">
+        <v>192.1</v>
+      </c>
+      <c r="L7" s="11">
+        <v>268.7</v>
+      </c>
+      <c r="M7" s="11">
+        <v>343.6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.75">
+      <c r="A8" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="B8" s="10" t="s">
+        <v>68</v>
+      </c>
+      <c r="C8" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="D8" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="E8" s="11">
+        <v>253.8999939</v>
+      </c>
+      <c r="F8" s="11">
+        <v>234.5</v>
+      </c>
+      <c r="G8" s="10">
+        <v>259</v>
+      </c>
+      <c r="H8" s="12">
+        <v>0.622</v>
+      </c>
+      <c r="I8" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="J8" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="K8" s="11">
+        <v>178.6</v>
+      </c>
+      <c r="L8" s="11">
+        <v>252.7</v>
+      </c>
+      <c r="M8" s="11">
+        <v>329.4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.75">
+      <c r="A9" s="10" t="s">
+        <v>106</v>
+      </c>
+      <c r="B9" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="C9" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="D9" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="E9" s="11">
+        <v>230.6000061</v>
+      </c>
+      <c r="F9" s="11">
+        <v>233.5</v>
+      </c>
+      <c r="G9" s="10">
+        <v>180</v>
+      </c>
+      <c r="H9" s="12">
+        <v>0.49199999999999999</v>
+      </c>
+      <c r="I9" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="J9" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="K9" s="11">
+        <v>155.30000000000001</v>
+      </c>
+      <c r="L9" s="11">
+        <v>232.3</v>
+      </c>
+      <c r="M9" s="11">
+        <v>306.60000000000002</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.75">
+      <c r="A10" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="B10" s="10" t="s">
+        <v>58</v>
+      </c>
+      <c r="C10" s="10" t="s">
+        <v>110</v>
+      </c>
+      <c r="D10" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="E10" s="11">
+        <v>232.3999939</v>
+      </c>
+      <c r="F10" s="11">
+        <v>248.5</v>
+      </c>
+      <c r="G10" s="10">
+        <v>264</v>
+      </c>
+      <c r="H10" s="12">
+        <v>0.379</v>
+      </c>
+      <c r="I10" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="J10" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="K10" s="11">
+        <v>157.4</v>
+      </c>
+      <c r="L10" s="11">
+        <v>230.7</v>
+      </c>
+      <c r="M10" s="11">
+        <v>305.2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.75">
+      <c r="A11" s="10" t="s">
+        <v>109</v>
+      </c>
+      <c r="B11" s="10" t="s">
+        <v>110</v>
+      </c>
+      <c r="C11" s="10" t="s">
+        <v>58</v>
+      </c>
+      <c r="D11" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="E11" s="11">
+        <v>232.6999969</v>
+      </c>
+      <c r="F11" s="11">
+        <v>220.5</v>
+      </c>
+      <c r="G11" s="10">
+        <v>205</v>
+      </c>
+      <c r="H11" s="12">
+        <v>0.58599999999999997</v>
+      </c>
+      <c r="I11" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="J11" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="K11" s="11">
+        <v>159.9</v>
+      </c>
+      <c r="L11" s="11">
+        <v>232.8</v>
+      </c>
+      <c r="M11" s="11">
+        <v>309.3</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.75">
+      <c r="A12" s="10" t="s">
+        <v>95</v>
+      </c>
+      <c r="B12" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="C12" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="D12" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="E12" s="11">
+        <v>256.5</v>
+      </c>
+      <c r="F12" s="11">
+        <v>259.5</v>
+      </c>
+      <c r="G12" s="10">
+        <v>257</v>
+      </c>
+      <c r="H12" s="12">
+        <v>0.47899999999999998</v>
+      </c>
+      <c r="I12" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="J12" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="K12" s="11">
+        <v>181.2</v>
+      </c>
+      <c r="L12" s="11">
+        <v>256.39999999999998</v>
+      </c>
+      <c r="M12" s="11">
+        <v>333.7</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.75">
+      <c r="A13" s="10" t="s">
+        <v>103</v>
+      </c>
+      <c r="B13" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="C13" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="D13" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="E13" s="11">
+        <v>246.6999969</v>
+      </c>
+      <c r="F13" s="11">
+        <v>235.5</v>
+      </c>
+      <c r="G13" s="10">
+        <v>203</v>
+      </c>
+      <c r="H13" s="12">
+        <v>0.56899999999999995</v>
+      </c>
+      <c r="I13" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="J13" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="K13" s="11">
+        <v>170.9</v>
+      </c>
+      <c r="L13" s="11">
+        <v>246.1</v>
+      </c>
+      <c r="M13" s="11">
+        <v>321.2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.75">
+      <c r="A14" s="10" t="s">
+        <v>128</v>
+      </c>
+      <c r="B14" s="10" t="s">
+        <v>100</v>
+      </c>
+      <c r="C14" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="D14" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="E14" s="11">
+        <v>221.6999969</v>
+      </c>
+      <c r="F14" s="11">
+        <v>220.5</v>
+      </c>
+      <c r="G14" s="10">
+        <v>227</v>
+      </c>
+      <c r="H14" s="12">
+        <v>0.504</v>
+      </c>
+      <c r="I14" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="J14" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="K14" s="11">
+        <v>146.1</v>
+      </c>
+      <c r="L14" s="11">
+        <v>220.9</v>
+      </c>
+      <c r="M14" s="11">
+        <v>296.39999999999998</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.75">
+      <c r="A15" s="10" t="s">
+        <v>81</v>
+      </c>
+      <c r="B15" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="C15" s="10" t="s">
+        <v>64</v>
+      </c>
+      <c r="D15" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="E15" s="11">
+        <v>226.6000061</v>
+      </c>
+      <c r="F15" s="11">
+        <v>223.5</v>
+      </c>
+      <c r="G15" s="10">
+        <v>199</v>
+      </c>
+      <c r="H15" s="12">
+        <v>0.52500000000000002</v>
+      </c>
+      <c r="I15" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="J15" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="K15" s="11">
+        <v>151.80000000000001</v>
+      </c>
+      <c r="L15" s="11">
+        <v>227.5</v>
+      </c>
+      <c r="M15" s="11">
+        <v>303.39999999999998</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.75">
+      <c r="A16" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="B16" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="C16" s="10" t="s">
+        <v>100</v>
+      </c>
+      <c r="D16" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="E16" s="11">
+        <v>248.6999969</v>
+      </c>
+      <c r="F16" s="11">
+        <v>235.5</v>
+      </c>
+      <c r="G16" s="10">
+        <v>261</v>
+      </c>
+      <c r="H16" s="12">
+        <v>0.58799999999999997</v>
+      </c>
+      <c r="I16" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="J16" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="K16" s="11">
+        <v>172.4</v>
+      </c>
+      <c r="L16" s="11">
+        <v>248.4</v>
+      </c>
+      <c r="M16" s="11">
+        <v>323.5</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" x14ac:dyDescent="0.75">
+      <c r="A17" s="10" t="s">
+        <v>133</v>
+      </c>
+      <c r="B17" s="10" t="s">
+        <v>111</v>
+      </c>
+      <c r="C17" s="10" t="s">
+        <v>99</v>
+      </c>
+      <c r="D17" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="E17" s="11">
+        <v>253.1999969</v>
+      </c>
+      <c r="F17" s="11">
+        <v>234.5</v>
+      </c>
+      <c r="G17" s="10">
+        <v>212</v>
+      </c>
+      <c r="H17" s="12">
+        <v>0.629</v>
+      </c>
+      <c r="I17" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="J17" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="K17" s="11">
+        <v>177.9</v>
+      </c>
+      <c r="L17" s="11">
+        <v>253.8</v>
+      </c>
+      <c r="M17" s="11">
+        <v>329.1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" x14ac:dyDescent="0.75">
+      <c r="A18" s="10" t="s">
+        <v>84</v>
+      </c>
+      <c r="B18" s="10" t="s">
+        <v>85</v>
+      </c>
+      <c r="C18" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="D18" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="E18" s="11">
+        <v>236</v>
+      </c>
+      <c r="F18" s="11">
+        <v>216.5</v>
+      </c>
+      <c r="G18" s="10">
+        <v>211</v>
+      </c>
+      <c r="H18" s="12">
+        <v>0.63200000000000001</v>
+      </c>
+      <c r="I18" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="J18" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="K18" s="11">
+        <v>160.5</v>
+      </c>
+      <c r="L18" s="11">
+        <v>236.3</v>
+      </c>
+      <c r="M18" s="11">
+        <v>312.2</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" x14ac:dyDescent="0.75">
+      <c r="A19" s="10" t="s">
+        <v>177</v>
+      </c>
+      <c r="B19" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="C19" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="D19" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="E19" s="11">
+        <v>255.8000031</v>
+      </c>
+      <c r="F19" s="11">
+        <v>246.5</v>
+      </c>
+      <c r="G19" s="10">
+        <v>347</v>
+      </c>
+      <c r="H19" s="12">
+        <v>0.56399999999999995</v>
+      </c>
+      <c r="I19" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="J19" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="K19" s="11">
+        <v>179.7</v>
+      </c>
+      <c r="L19" s="11">
+        <v>256.2</v>
+      </c>
+      <c r="M19" s="11">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" x14ac:dyDescent="0.75">
+      <c r="A20" s="10" t="s">
+        <v>119</v>
+      </c>
+      <c r="B20" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="C20" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="D20" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="E20" s="11">
+        <v>247.6000061</v>
+      </c>
+      <c r="F20" s="11">
+        <v>240.5</v>
+      </c>
+      <c r="G20" s="10">
+        <v>256</v>
+      </c>
+      <c r="H20" s="12">
+        <v>0.54700000000000004</v>
+      </c>
+      <c r="I20" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="J20" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="K20" s="11">
+        <v>172.2</v>
+      </c>
+      <c r="L20" s="11">
+        <v>247.2</v>
+      </c>
+      <c r="M20" s="11">
+        <v>323.8</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13" x14ac:dyDescent="0.75">
+      <c r="A21" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="B21" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="C21" s="10" t="s">
+        <v>85</v>
+      </c>
+      <c r="D21" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="E21" s="11">
+        <v>245.8000031</v>
+      </c>
+      <c r="F21" s="11">
+        <v>235.5</v>
+      </c>
+      <c r="G21" s="10">
+        <v>252</v>
+      </c>
+      <c r="H21" s="12">
+        <v>0.57299999999999995</v>
+      </c>
+      <c r="I21" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="J21" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="K21" s="11">
+        <v>169.7</v>
+      </c>
+      <c r="L21" s="11">
+        <v>246.5</v>
+      </c>
+      <c r="M21" s="11">
+        <v>322.10000000000002</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13" x14ac:dyDescent="0.75">
+      <c r="A22" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="B22" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="C22" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="D22" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="E22" s="11">
+        <v>248</v>
+      </c>
+      <c r="F22" s="11">
+        <v>237.5</v>
+      </c>
+      <c r="G22" s="10">
+        <v>295</v>
+      </c>
+      <c r="H22" s="12">
+        <v>0.56599999999999995</v>
+      </c>
+      <c r="I22" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="J22" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="K22" s="11">
+        <v>173.5</v>
+      </c>
+      <c r="L22" s="11">
+        <v>246.9</v>
+      </c>
+      <c r="M22" s="11">
+        <v>323.2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13" x14ac:dyDescent="0.75">
+      <c r="A23" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="B23" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="C23" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="D23" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="E23" s="11">
+        <v>240.1000061</v>
+      </c>
+      <c r="F23" s="11">
+        <v>228.5</v>
+      </c>
+      <c r="G23" s="10">
+        <v>258</v>
+      </c>
+      <c r="H23" s="12">
+        <v>0.57299999999999995</v>
+      </c>
+      <c r="I23" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="J23" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="K23" s="11">
+        <v>164</v>
+      </c>
+      <c r="L23" s="11">
+        <v>239.3</v>
+      </c>
+      <c r="M23" s="11">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13" x14ac:dyDescent="0.75">
+      <c r="A24" s="10" t="s">
+        <v>131</v>
+      </c>
+      <c r="B24" s="10" t="s">
+        <v>64</v>
+      </c>
+      <c r="C24" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="D24" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="E24" s="11">
+        <v>269.7000122</v>
+      </c>
+      <c r="F24" s="11">
+        <v>245.5</v>
+      </c>
+      <c r="G24" s="10">
+        <v>261</v>
+      </c>
+      <c r="H24" s="12">
+        <v>0.65600000000000003</v>
+      </c>
+      <c r="I24" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="J24" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="K24" s="11">
+        <v>193.9</v>
+      </c>
+      <c r="L24" s="11">
+        <v>269.2</v>
+      </c>
+      <c r="M24" s="11">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13" x14ac:dyDescent="0.75">
+      <c r="A25" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="B25" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="C25" s="10" t="s">
+        <v>68</v>
+      </c>
+      <c r="D25" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="E25" s="11">
+        <v>215.6999969</v>
+      </c>
+      <c r="F25" s="11">
+        <v>206.5</v>
+      </c>
+      <c r="G25" s="10">
+        <v>219</v>
+      </c>
+      <c r="H25" s="12">
+        <v>0.55700000000000005</v>
+      </c>
+      <c r="I25" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="J25" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="K25" s="11">
+        <v>140.69999999999999</v>
+      </c>
+      <c r="L25" s="11">
+        <v>215.2</v>
+      </c>
+      <c r="M25" s="11">
+        <v>291.60000000000002</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
+  <dimension ref="A1:M4"/>
+  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
+  <cols>
+    <col min="1" max="1" width="11" customWidth="1"/>
+    <col min="2" max="2" width="6" customWidth="1"/>
+    <col min="3" max="3" width="10" customWidth="1"/>
+    <col min="4" max="5" width="11" customWidth="1"/>
+    <col min="6" max="6" width="12" customWidth="1"/>
+    <col min="7" max="7" width="8" customWidth="1"/>
+    <col min="8" max="8" width="11" customWidth="1"/>
+    <col min="9" max="9" width="7" customWidth="1"/>
+    <col min="10" max="10" width="6" customWidth="1"/>
+    <col min="11" max="13" width="7" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13" x14ac:dyDescent="0.75">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.75">
+      <c r="A2" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="B2" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="C2" s="13" t="s">
+        <v>78</v>
+      </c>
+      <c r="D2" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="E2" s="13">
+        <v>218</v>
+      </c>
+      <c r="F2" s="13">
+        <v>232.5</v>
+      </c>
+      <c r="G2" s="13"/>
+      <c r="H2" s="13" t="s">
         <v>279</v>
       </c>
-      <c r="F1" s="8" t="s">
-        <v>280</v>
-      </c>
-      <c r="G1" s="8" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="8" t="s">
-        <v>281</v>
-      </c>
-      <c r="I1" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" s="8" t="s">
-        <v>282</v>
-      </c>
-      <c r="K1" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="L1" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="M1" s="8" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13" ht="16.75" customHeight="1" x14ac:dyDescent="0.75">
-      <c r="A2" s="9" t="s">
-        <v>40</v>
-      </c>
-      <c r="B2" s="9" t="s">
-        <v>41</v>
-      </c>
-      <c r="C2" s="9" t="s">
-        <v>99</v>
-      </c>
-      <c r="D2" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="E2" s="10">
-        <v>218.3999939</v>
-      </c>
-      <c r="F2" s="10">
-        <v>228.5</v>
-      </c>
-      <c r="G2" s="9"/>
-      <c r="H2" s="11">
-        <v>0.437</v>
-      </c>
-      <c r="I2" s="12" t="s">
-        <v>24</v>
-      </c>
-      <c r="J2" s="9"/>
-      <c r="K2" s="10">
-        <v>142.1</v>
-      </c>
-      <c r="L2" s="10">
-        <v>218.6</v>
-      </c>
-      <c r="M2" s="10">
-        <v>296</v>
+      <c r="I2" s="14" t="s">
+        <v>26</v>
+      </c>
+      <c r="J2" s="13"/>
+      <c r="K2" s="13">
+        <v>142.6</v>
+      </c>
+      <c r="L2" s="13">
+        <v>219.1</v>
+      </c>
+      <c r="M2" s="13">
+        <v>294</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.75">
-      <c r="A3" s="9" t="s">
-        <v>55</v>
-      </c>
-      <c r="B3" s="9" t="s">
-        <v>56</v>
-      </c>
-      <c r="C3" s="9" t="s">
-        <v>74</v>
-      </c>
-      <c r="D3" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="E3" s="10">
-        <v>233.6000061</v>
-      </c>
-      <c r="F3" s="10">
-        <v>196.5</v>
-      </c>
-      <c r="G3" s="9"/>
-      <c r="H3" s="11">
-        <v>0.73399999999999999</v>
-      </c>
-      <c r="I3" s="13" t="s">
-        <v>18</v>
-      </c>
-      <c r="J3" s="9"/>
-      <c r="K3" s="10">
-        <v>156.9</v>
-      </c>
-      <c r="L3" s="10">
-        <v>233.5</v>
-      </c>
-      <c r="M3" s="10">
-        <v>308.3</v>
+      <c r="A3" s="13" t="s">
+        <v>136</v>
+      </c>
+      <c r="B3" s="13" t="s">
+        <v>78</v>
+      </c>
+      <c r="C3" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="D3" s="13" t="s">
+        <v>31</v>
+      </c>
+      <c r="E3" s="13">
+        <v>224.5</v>
+      </c>
+      <c r="F3" s="13">
+        <v>216.5</v>
+      </c>
+      <c r="G3" s="13"/>
+      <c r="H3" s="13" t="s">
+        <v>83</v>
+      </c>
+      <c r="I3" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="J3" s="13"/>
+      <c r="K3" s="13">
+        <v>150.1</v>
+      </c>
+      <c r="L3" s="13">
+        <v>224.5</v>
+      </c>
+      <c r="M3" s="13">
+        <v>300.3</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.75">
-      <c r="A4" s="9" t="s">
-        <v>97</v>
-      </c>
-      <c r="B4" s="9" t="s">
-        <v>98</v>
-      </c>
-      <c r="C4" s="9" t="s">
-        <v>67</v>
-      </c>
-      <c r="D4" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="E4" s="10">
-        <v>237.8999939</v>
-      </c>
-      <c r="F4" s="10">
-        <v>223.5</v>
-      </c>
-      <c r="G4" s="9"/>
-      <c r="H4" s="11">
-        <v>0.59199999999999997</v>
-      </c>
-      <c r="I4" s="13" t="s">
-        <v>18</v>
-      </c>
-      <c r="J4" s="9"/>
-      <c r="K4" s="10">
-        <v>162</v>
-      </c>
-      <c r="L4" s="10">
-        <v>237.2</v>
-      </c>
-      <c r="M4" s="10">
-        <v>313.7</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.75">
-      <c r="A5" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="B5" s="9" t="s">
-        <v>67</v>
-      </c>
-      <c r="C5" s="9" t="s">
-        <v>98</v>
-      </c>
-      <c r="D5" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="E5" s="10">
-        <v>215.6000061</v>
-      </c>
-      <c r="F5" s="10">
-        <v>197.5</v>
-      </c>
-      <c r="G5" s="9"/>
-      <c r="H5" s="11">
-        <v>0.61399999999999999</v>
-      </c>
-      <c r="I5" s="13" t="s">
-        <v>18</v>
-      </c>
-      <c r="J5" s="9"/>
-      <c r="K5" s="10">
-        <v>140.1</v>
-      </c>
-      <c r="L5" s="10">
-        <v>215.8</v>
-      </c>
-      <c r="M5" s="10">
-        <v>292</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.75">
-      <c r="A6" s="9" t="s">
-        <v>114</v>
-      </c>
-      <c r="B6" s="9" t="s">
-        <v>68</v>
-      </c>
-      <c r="C6" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="D6" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="E6" s="10">
-        <v>216.5</v>
-      </c>
-      <c r="F6" s="10">
-        <v>206.5</v>
-      </c>
-      <c r="G6" s="9"/>
-      <c r="H6" s="11">
-        <v>0.56599999999999995</v>
-      </c>
-      <c r="I6" s="13" t="s">
-        <v>18</v>
-      </c>
-      <c r="J6" s="9"/>
-      <c r="K6" s="10">
-        <v>139.19999999999999</v>
-      </c>
-      <c r="L6" s="10">
-        <v>216.9</v>
-      </c>
-      <c r="M6" s="10">
-        <v>290.89999999999998</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.75">
-      <c r="A7" s="9" t="s">
-        <v>80</v>
-      </c>
-      <c r="B7" s="9" t="s">
-        <v>65</v>
-      </c>
-      <c r="C7" s="9" t="s">
-        <v>27</v>
-      </c>
-      <c r="D7" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="E7" s="10">
-        <v>267.2000122</v>
-      </c>
-      <c r="F7" s="10">
-        <v>262.5</v>
-      </c>
-      <c r="G7" s="9"/>
-      <c r="H7" s="11">
-        <v>0.54500000000000004</v>
-      </c>
-      <c r="I7" s="13" t="s">
-        <v>18</v>
-      </c>
-      <c r="J7" s="9"/>
-      <c r="K7" s="10">
-        <v>192.1</v>
-      </c>
-      <c r="L7" s="10">
-        <v>268.7</v>
-      </c>
-      <c r="M7" s="10">
-        <v>343.6</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.75">
-      <c r="A8" s="9" t="s">
-        <v>59</v>
-      </c>
-      <c r="B8" s="9" t="s">
-        <v>60</v>
-      </c>
-      <c r="C8" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="D8" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="E8" s="10">
-        <v>253.8999939</v>
-      </c>
-      <c r="F8" s="10">
-        <v>234.5</v>
-      </c>
-      <c r="G8" s="9"/>
-      <c r="H8" s="11">
-        <v>0.622</v>
-      </c>
-      <c r="I8" s="13" t="s">
-        <v>18</v>
-      </c>
-      <c r="J8" s="9"/>
-      <c r="K8" s="10">
-        <v>178.6</v>
-      </c>
-      <c r="L8" s="10">
-        <v>252.7</v>
-      </c>
-      <c r="M8" s="10">
-        <v>329.4</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.75">
-      <c r="A9" s="9" t="s">
-        <v>91</v>
-      </c>
-      <c r="B9" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="C9" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="D9" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="E9" s="10">
-        <v>230.6000061</v>
-      </c>
-      <c r="F9" s="10">
-        <v>233.5</v>
-      </c>
-      <c r="G9" s="9"/>
-      <c r="H9" s="11">
-        <v>0.49199999999999999</v>
-      </c>
-      <c r="I9" s="12" t="s">
-        <v>24</v>
-      </c>
-      <c r="J9" s="9"/>
-      <c r="K9" s="10">
-        <v>155.30000000000001</v>
-      </c>
-      <c r="L9" s="10">
-        <v>232.3</v>
-      </c>
-      <c r="M9" s="10">
-        <v>306.60000000000002</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.75">
-      <c r="A10" s="9" t="s">
-        <v>50</v>
-      </c>
-      <c r="B10" s="9" t="s">
-        <v>51</v>
-      </c>
-      <c r="C10" s="9" t="s">
-        <v>94</v>
-      </c>
-      <c r="D10" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="E10" s="10">
-        <v>232.3999939</v>
-      </c>
-      <c r="F10" s="10">
-        <v>248.5</v>
-      </c>
-      <c r="G10" s="9"/>
-      <c r="H10" s="11">
-        <v>0.379</v>
-      </c>
-      <c r="I10" s="12" t="s">
-        <v>24</v>
-      </c>
-      <c r="J10" s="9"/>
-      <c r="K10" s="10">
-        <v>157.4</v>
-      </c>
-      <c r="L10" s="10">
-        <v>230.7</v>
-      </c>
-      <c r="M10" s="10">
-        <v>305.2</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.75">
-      <c r="A11" s="9" t="s">
-        <v>93</v>
-      </c>
-      <c r="B11" s="9" t="s">
-        <v>94</v>
-      </c>
-      <c r="C11" s="9" t="s">
-        <v>51</v>
-      </c>
-      <c r="D11" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="E11" s="10">
-        <v>232.6999969</v>
-      </c>
-      <c r="F11" s="10">
-        <v>220.5</v>
-      </c>
-      <c r="G11" s="9"/>
-      <c r="H11" s="11">
-        <v>0.58599999999999997</v>
-      </c>
-      <c r="I11" s="13" t="s">
-        <v>18</v>
-      </c>
-      <c r="J11" s="9"/>
-      <c r="K11" s="10">
-        <v>159.9</v>
-      </c>
-      <c r="L11" s="10">
-        <v>232.8</v>
-      </c>
-      <c r="M11" s="10">
-        <v>309.3</v>
-      </c>
-    </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.75">
-      <c r="A12" s="9" t="s">
-        <v>82</v>
-      </c>
-      <c r="B12" s="9" t="s">
-        <v>52</v>
-      </c>
-      <c r="C12" s="9" t="s">
-        <v>61</v>
-      </c>
-      <c r="D12" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="E12" s="10">
-        <v>256.5</v>
-      </c>
-      <c r="F12" s="10">
-        <v>259.5</v>
-      </c>
-      <c r="G12" s="9"/>
-      <c r="H12" s="11">
-        <v>0.47899999999999998</v>
-      </c>
-      <c r="I12" s="12" t="s">
-        <v>24</v>
-      </c>
-      <c r="J12" s="9"/>
-      <c r="K12" s="10">
-        <v>181.2</v>
-      </c>
-      <c r="L12" s="10">
-        <v>256.39999999999998</v>
-      </c>
-      <c r="M12" s="10">
-        <v>333.7</v>
-      </c>
-    </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.75">
-      <c r="A13" s="9" t="s">
-        <v>89</v>
-      </c>
-      <c r="B13" s="9" t="s">
-        <v>61</v>
-      </c>
-      <c r="C13" s="9" t="s">
-        <v>52</v>
-      </c>
-      <c r="D13" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="E13" s="10">
-        <v>246.6999969</v>
-      </c>
-      <c r="F13" s="10">
-        <v>235.5</v>
-      </c>
-      <c r="G13" s="9"/>
-      <c r="H13" s="11">
-        <v>0.56899999999999995</v>
-      </c>
-      <c r="I13" s="13" t="s">
-        <v>18</v>
-      </c>
-      <c r="J13" s="9"/>
-      <c r="K13" s="10">
-        <v>170.9</v>
-      </c>
-      <c r="L13" s="10">
-        <v>246.1</v>
-      </c>
-      <c r="M13" s="10">
-        <v>321.2</v>
-      </c>
-    </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.75">
-      <c r="A14" s="9" t="s">
-        <v>108</v>
-      </c>
-      <c r="B14" s="9" t="s">
-        <v>86</v>
-      </c>
-      <c r="C14" s="9" t="s">
-        <v>42</v>
-      </c>
-      <c r="D14" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="E14" s="10">
-        <v>221.6999969</v>
-      </c>
-      <c r="F14" s="10">
-        <v>220.5</v>
-      </c>
-      <c r="G14" s="9"/>
-      <c r="H14" s="11">
-        <v>0.504</v>
-      </c>
-      <c r="I14" s="13" t="s">
-        <v>18</v>
-      </c>
-      <c r="J14" s="9"/>
-      <c r="K14" s="10">
-        <v>146.1</v>
-      </c>
-      <c r="L14" s="10">
-        <v>220.9</v>
-      </c>
-      <c r="M14" s="10">
-        <v>296.39999999999998</v>
-      </c>
-    </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.75">
-      <c r="A15" s="9" t="s">
-        <v>70</v>
-      </c>
-      <c r="B15" s="9" t="s">
-        <v>46</v>
-      </c>
-      <c r="C15" s="9" t="s">
-        <v>57</v>
-      </c>
-      <c r="D15" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="E15" s="10">
-        <v>226.6000061</v>
-      </c>
-      <c r="F15" s="10">
-        <v>223.5</v>
-      </c>
-      <c r="G15" s="9"/>
-      <c r="H15" s="11">
-        <v>0.52500000000000002</v>
-      </c>
-      <c r="I15" s="13" t="s">
-        <v>18</v>
-      </c>
-      <c r="J15" s="9"/>
-      <c r="K15" s="10">
-        <v>151.80000000000001</v>
-      </c>
-      <c r="L15" s="10">
-        <v>227.5</v>
-      </c>
-      <c r="M15" s="10">
-        <v>303.39999999999998</v>
-      </c>
-    </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.75">
-      <c r="A16" s="9" t="s">
-        <v>48</v>
-      </c>
-      <c r="B16" s="9" t="s">
-        <v>42</v>
-      </c>
-      <c r="C16" s="9" t="s">
-        <v>86</v>
-      </c>
-      <c r="D16" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="E16" s="10">
-        <v>248.6999969</v>
-      </c>
-      <c r="F16" s="10">
-        <v>235.5</v>
-      </c>
-      <c r="G16" s="9"/>
-      <c r="H16" s="11">
-        <v>0.58799999999999997</v>
-      </c>
-      <c r="I16" s="13" t="s">
-        <v>18</v>
-      </c>
-      <c r="J16" s="9"/>
-      <c r="K16" s="10">
-        <v>172.4</v>
-      </c>
-      <c r="L16" s="10">
-        <v>248.4</v>
-      </c>
-      <c r="M16" s="10">
-        <v>323.5</v>
-      </c>
-    </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.75">
-      <c r="A17" s="9" t="s">
-        <v>112</v>
-      </c>
-      <c r="B17" s="9" t="s">
-        <v>95</v>
-      </c>
-      <c r="C17" s="9" t="s">
-        <v>85</v>
-      </c>
-      <c r="D17" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="E17" s="10">
-        <v>253.1999969</v>
-      </c>
-      <c r="F17" s="10">
-        <v>234.5</v>
-      </c>
-      <c r="G17" s="9"/>
-      <c r="H17" s="11">
-        <v>0.629</v>
-      </c>
-      <c r="I17" s="13" t="s">
-        <v>18</v>
-      </c>
-      <c r="J17" s="9"/>
-      <c r="K17" s="10">
-        <v>177.9</v>
-      </c>
-      <c r="L17" s="10">
-        <v>253.8</v>
-      </c>
-      <c r="M17" s="10">
-        <v>329.1</v>
-      </c>
-    </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.75">
-      <c r="A18" s="9" t="s">
-        <v>72</v>
-      </c>
-      <c r="B18" s="9" t="s">
-        <v>73</v>
-      </c>
-      <c r="C18" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="D18" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="E18" s="10">
-        <v>236</v>
-      </c>
-      <c r="F18" s="10">
-        <v>216.5</v>
-      </c>
-      <c r="G18" s="9"/>
-      <c r="H18" s="11">
-        <v>0.63200000000000001</v>
-      </c>
-      <c r="I18" s="13" t="s">
-        <v>18</v>
-      </c>
-      <c r="J18" s="9"/>
-      <c r="K18" s="10">
-        <v>160.5</v>
-      </c>
-      <c r="L18" s="10">
-        <v>236.3</v>
-      </c>
-      <c r="M18" s="10">
-        <v>312.2</v>
-      </c>
-    </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.75">
-      <c r="A19" s="9" t="s">
-        <v>167</v>
-      </c>
-      <c r="B19" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="C19" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="D19" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="E19" s="10">
-        <v>255.8000031</v>
-      </c>
-      <c r="F19" s="10">
-        <v>246.5</v>
-      </c>
-      <c r="G19" s="9"/>
-      <c r="H19" s="11">
-        <v>0.56399999999999995</v>
-      </c>
-      <c r="I19" s="13" t="s">
-        <v>18</v>
-      </c>
-      <c r="J19" s="9"/>
-      <c r="K19" s="10">
-        <v>179.7</v>
-      </c>
-      <c r="L19" s="10">
-        <v>256.2</v>
-      </c>
-      <c r="M19" s="10">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.75">
-      <c r="A20" s="9" t="s">
-        <v>101</v>
-      </c>
-      <c r="B20" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="C20" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="D20" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="E20" s="10">
-        <v>247.6000061</v>
-      </c>
-      <c r="F20" s="10">
-        <v>240.5</v>
-      </c>
-      <c r="G20" s="9"/>
-      <c r="H20" s="11">
-        <v>0.54700000000000004</v>
-      </c>
-      <c r="I20" s="13" t="s">
-        <v>18</v>
-      </c>
-      <c r="J20" s="9"/>
-      <c r="K20" s="10">
-        <v>172.2</v>
-      </c>
-      <c r="L20" s="10">
-        <v>247.2</v>
-      </c>
-      <c r="M20" s="10">
-        <v>323.8</v>
-      </c>
-    </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.75">
-      <c r="A21" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="B21" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="C21" s="9" t="s">
-        <v>73</v>
-      </c>
-      <c r="D21" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="E21" s="10">
-        <v>245.8000031</v>
-      </c>
-      <c r="F21" s="10">
-        <v>235.5</v>
-      </c>
-      <c r="G21" s="9"/>
-      <c r="H21" s="11">
-        <v>0.57299999999999995</v>
-      </c>
-      <c r="I21" s="13" t="s">
-        <v>18</v>
-      </c>
-      <c r="J21" s="9"/>
-      <c r="K21" s="10">
-        <v>169.7</v>
-      </c>
-      <c r="L21" s="10">
-        <v>246.5</v>
-      </c>
-      <c r="M21" s="10">
-        <v>322.10000000000002</v>
-      </c>
-    </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.75">
-      <c r="A22" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="B22" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="C22" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="D22" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="E22" s="10">
-        <v>248</v>
-      </c>
-      <c r="F22" s="10">
-        <v>237.5</v>
-      </c>
-      <c r="G22" s="9"/>
-      <c r="H22" s="11">
-        <v>0.56599999999999995</v>
-      </c>
-      <c r="I22" s="13" t="s">
-        <v>18</v>
-      </c>
-      <c r="J22" s="9"/>
-      <c r="K22" s="10">
-        <v>173.5</v>
-      </c>
-      <c r="L22" s="10">
-        <v>246.9</v>
-      </c>
-      <c r="M22" s="10">
-        <v>323.2</v>
-      </c>
-    </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.75">
-      <c r="A23" s="9" t="s">
-        <v>44</v>
-      </c>
-      <c r="B23" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="C23" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="D23" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="E23" s="10">
-        <v>240.1000061</v>
-      </c>
-      <c r="F23" s="10">
-        <v>228.5</v>
-      </c>
-      <c r="G23" s="9"/>
-      <c r="H23" s="11">
-        <v>0.57299999999999995</v>
-      </c>
-      <c r="I23" s="13" t="s">
-        <v>18</v>
-      </c>
-      <c r="J23" s="9"/>
-      <c r="K23" s="10">
-        <v>164</v>
-      </c>
-      <c r="L23" s="10">
-        <v>239.3</v>
-      </c>
-      <c r="M23" s="10">
-        <v>315</v>
-      </c>
-    </row>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.75">
-      <c r="A24" s="9" t="s">
-        <v>111</v>
-      </c>
-      <c r="B24" s="9" t="s">
-        <v>57</v>
-      </c>
-      <c r="C24" s="9" t="s">
-        <v>46</v>
-      </c>
-      <c r="D24" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="E24" s="10">
-        <v>269.7000122</v>
-      </c>
-      <c r="F24" s="10">
-        <v>245.5</v>
-      </c>
-      <c r="G24" s="9"/>
-      <c r="H24" s="11">
-        <v>0.65600000000000003</v>
-      </c>
-      <c r="I24" s="13" t="s">
-        <v>18</v>
-      </c>
-      <c r="J24" s="9"/>
-      <c r="K24" s="10">
-        <v>193.9</v>
-      </c>
-      <c r="L24" s="10">
-        <v>269.2</v>
-      </c>
-      <c r="M24" s="10">
-        <v>346</v>
-      </c>
-    </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.75">
-      <c r="A25" s="9" t="s">
-        <v>31</v>
-      </c>
-      <c r="B25" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="C25" s="9" t="s">
-        <v>60</v>
-      </c>
-      <c r="D25" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="E25" s="10">
-        <v>215.6999969</v>
-      </c>
-      <c r="F25" s="10">
-        <v>206.5</v>
-      </c>
-      <c r="G25" s="9"/>
-      <c r="H25" s="11">
-        <v>0.55700000000000005</v>
-      </c>
-      <c r="I25" s="13" t="s">
-        <v>18</v>
-      </c>
-      <c r="J25" s="9"/>
-      <c r="K25" s="10">
-        <v>140.69999999999999</v>
-      </c>
-      <c r="L25" s="10">
-        <v>215.2</v>
-      </c>
-      <c r="M25" s="10">
-        <v>291.60000000000002</v>
-      </c>
+      <c r="A4" s="13"/>
+      <c r="B4" s="13"/>
+      <c r="C4" s="13"/>
+      <c r="D4" s="13"/>
+      <c r="E4" s="13"/>
+      <c r="F4" s="13"/>
+      <c r="G4" s="13"/>
+      <c r="H4" s="13"/>
+      <c r="I4" s="13"/>
+      <c r="J4" s="13"/>
+      <c r="K4" s="13"/>
+      <c r="L4" s="13"/>
+      <c r="M4" s="13"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/passing-prop-predictions-2025.xlsx
+++ b/data/passing-prop-predictions-2025.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/98038a0616e2a1bf/Desktop/Development/Projects/nfl-prop-model-2/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="11_04E55082DCEDC07E2FDAD079445BB426E960B561" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{324E5CDE-CF0A-4F50-9E2E-CAFDAF0F1BB4}"/>
+  <xr:revisionPtr revIDLastSave="3" documentId="11_2BDDA100C818C55DB68CC132954B5956B0404189" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4152FBA0-E3D6-4271-A9D8-F3D4EC37FA82}"/>
   <bookViews>
-    <workbookView xWindow="-90" yWindow="-90" windowWidth="19380" windowHeight="10260" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-90" yWindow="-90" windowWidth="19380" windowHeight="10260" firstSheet="2" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Week 1" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1237" uniqueCount="280">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1333" uniqueCount="285">
   <si>
     <t>Player</t>
   </si>
@@ -865,14 +865,29 @@
     <t>58.5%</t>
   </si>
   <si>
-    <t>40.7%</t>
+    <t>55.4%</t>
+  </si>
+  <si>
+    <t>57.8%</t>
+  </si>
+  <si>
+    <t>58.0%</t>
+  </si>
+  <si>
+    <t>56.5%</t>
+  </si>
+  <si>
+    <t>58.8%</t>
+  </si>
+  <si>
+    <t>61.4%</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -896,8 +911,13 @@
       <color theme="1"/>
       <name val="Arial"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
   </fonts>
-  <fills count="8">
+  <fills count="13">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -940,6 +960,36 @@
         <bgColor rgb="FF90EE90"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF90EE90"/>
+        <bgColor rgb="FF90EE90"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF90EE90"/>
+        <bgColor rgb="FF90EE90"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF90EE90"/>
+        <bgColor rgb="FF90EE90"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF90EE90"/>
+        <bgColor rgb="FF90EE90"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF90EE90"/>
+        <bgColor rgb="FF90EE90"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -953,7 +1003,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -996,6 +1046,24 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1222,7 +1290,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-468D-4FDC-8D47-23D4A658F5FA}"/>
+              <c16:uniqueId val="{00000000-0F74-479D-8B89-D2F319169077}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1401,7 +1469,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-468D-4FDC-8D47-23D4A658F5FA}"/>
+              <c16:uniqueId val="{00000001-0F74-479D-8B89-D2F319169077}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -38842,59 +38910,60 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
-  <dimension ref="A1:M4"/>
+  <dimension ref="A1:M19"/>
   <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
   <cols>
-    <col min="1" max="1" width="11" customWidth="1"/>
+    <col min="1" max="1" width="14" customWidth="1"/>
     <col min="2" max="2" width="6" customWidth="1"/>
     <col min="3" max="3" width="10" customWidth="1"/>
-    <col min="4" max="5" width="11" customWidth="1"/>
+    <col min="4" max="4" width="11" customWidth="1"/>
+    <col min="5" max="5" width="20" customWidth="1"/>
     <col min="6" max="6" width="12" customWidth="1"/>
     <col min="7" max="7" width="8" customWidth="1"/>
     <col min="8" max="8" width="11" customWidth="1"/>
     <col min="9" max="9" width="7" customWidth="1"/>
-    <col min="10" max="10" width="6" customWidth="1"/>
+    <col min="10" max="10" width="10" customWidth="1"/>
     <col min="11" max="13" width="7" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.75">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="20" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="20" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="20" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="20" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="20" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="20" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="20" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="I1" s="20" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="J1" s="20" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="K1" s="20" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="L1" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="M1" s="20" t="s">
         <v>12</v>
       </c>
     </row>
@@ -38919,20 +38988,20 @@
       </c>
       <c r="G2" s="13"/>
       <c r="H2" s="13" t="s">
-        <v>279</v>
+        <v>220</v>
       </c>
       <c r="I2" s="14" t="s">
         <v>26</v>
       </c>
       <c r="J2" s="13"/>
       <c r="K2" s="13">
-        <v>142.6</v>
+        <v>143.19999999999999</v>
       </c>
       <c r="L2" s="13">
-        <v>219.1</v>
+        <v>218</v>
       </c>
       <c r="M2" s="13">
-        <v>294</v>
+        <v>293.7</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.75">
@@ -38956,36 +39025,613 @@
       </c>
       <c r="G3" s="13"/>
       <c r="H3" s="13" t="s">
-        <v>83</v>
+        <v>279</v>
       </c>
       <c r="I3" s="15" t="s">
         <v>19</v>
       </c>
       <c r="J3" s="13"/>
       <c r="K3" s="13">
-        <v>150.1</v>
+        <v>150.6</v>
       </c>
       <c r="L3" s="13">
-        <v>224.5</v>
+        <v>224.1</v>
       </c>
       <c r="M3" s="13">
-        <v>300.3</v>
+        <v>297.60000000000002</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.75">
-      <c r="A4" s="13"/>
-      <c r="B4" s="13"/>
-      <c r="C4" s="13"/>
-      <c r="D4" s="13"/>
-      <c r="E4" s="13"/>
-      <c r="F4" s="13"/>
+      <c r="A4" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="B4" s="13" t="s">
+        <v>74</v>
+      </c>
+      <c r="C4" s="13" t="s">
+        <v>50</v>
+      </c>
+      <c r="D4" s="13" t="s">
+        <v>31</v>
+      </c>
+      <c r="E4" s="13">
+        <v>261.39999389648438</v>
+      </c>
+      <c r="F4" s="13">
+        <v>250.5</v>
+      </c>
       <c r="G4" s="13"/>
-      <c r="H4" s="13"/>
-      <c r="I4" s="13"/>
+      <c r="H4" s="13" t="s">
+        <v>280</v>
+      </c>
+      <c r="I4" s="15" t="s">
+        <v>19</v>
+      </c>
       <c r="J4" s="13"/>
-      <c r="K4" s="13"/>
-      <c r="L4" s="13"/>
-      <c r="M4" s="13"/>
+      <c r="K4" s="13">
+        <v>186.4</v>
+      </c>
+      <c r="L4" s="13">
+        <v>262.10000000000002</v>
+      </c>
+      <c r="M4" s="13">
+        <v>337.1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.75">
+      <c r="A5" s="13" t="s">
+        <v>49</v>
+      </c>
+      <c r="B5" s="13" t="s">
+        <v>50</v>
+      </c>
+      <c r="C5" s="13" t="s">
+        <v>74</v>
+      </c>
+      <c r="D5" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="E5" s="13">
+        <v>234.30000305175781</v>
+      </c>
+      <c r="F5" s="13">
+        <v>222.5</v>
+      </c>
+      <c r="G5" s="13"/>
+      <c r="H5" s="13" t="s">
+        <v>281</v>
+      </c>
+      <c r="I5" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="J5" s="13"/>
+      <c r="K5" s="13">
+        <v>158</v>
+      </c>
+      <c r="L5" s="13">
+        <v>233.9</v>
+      </c>
+      <c r="M5" s="13">
+        <v>311.39999999999998</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.75">
+      <c r="A6" s="13" t="s">
+        <v>114</v>
+      </c>
+      <c r="B6" s="13" t="s">
+        <v>115</v>
+      </c>
+      <c r="C6" s="13" t="s">
+        <v>86</v>
+      </c>
+      <c r="D6" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="E6" s="13">
+        <v>233.69999694824219</v>
+      </c>
+      <c r="F6" s="13">
+        <v>218.5</v>
+      </c>
+      <c r="G6" s="13"/>
+      <c r="H6" s="13" t="s">
+        <v>61</v>
+      </c>
+      <c r="I6" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="J6" s="13"/>
+      <c r="K6" s="13">
+        <v>158.69999999999999</v>
+      </c>
+      <c r="L6" s="13">
+        <v>233</v>
+      </c>
+      <c r="M6" s="13">
+        <v>308.2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.75">
+      <c r="A7" s="13" t="s">
+        <v>81</v>
+      </c>
+      <c r="B7" s="13" t="s">
+        <v>51</v>
+      </c>
+      <c r="C7" s="13" t="s">
+        <v>77</v>
+      </c>
+      <c r="D7" s="13" t="s">
+        <v>31</v>
+      </c>
+      <c r="E7" s="13">
+        <v>222.6000061035156</v>
+      </c>
+      <c r="F7" s="13">
+        <v>194.5</v>
+      </c>
+      <c r="G7" s="13"/>
+      <c r="H7" s="13" t="s">
+        <v>201</v>
+      </c>
+      <c r="I7" s="18" t="s">
+        <v>19</v>
+      </c>
+      <c r="J7" s="13"/>
+      <c r="K7" s="13">
+        <v>144.9</v>
+      </c>
+      <c r="L7" s="13">
+        <v>221.4</v>
+      </c>
+      <c r="M7" s="13">
+        <v>297.5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.75">
+      <c r="A8" s="13" t="s">
+        <v>76</v>
+      </c>
+      <c r="B8" s="13" t="s">
+        <v>77</v>
+      </c>
+      <c r="C8" s="13" t="s">
+        <v>51</v>
+      </c>
+      <c r="D8" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="E8" s="13">
+        <v>206</v>
+      </c>
+      <c r="F8" s="13">
+        <v>176.5</v>
+      </c>
+      <c r="G8" s="13"/>
+      <c r="H8" s="13" t="s">
+        <v>143</v>
+      </c>
+      <c r="I8" s="18" t="s">
+        <v>19</v>
+      </c>
+      <c r="J8" s="13"/>
+      <c r="K8" s="13">
+        <v>130.4</v>
+      </c>
+      <c r="L8" s="13">
+        <v>206.2</v>
+      </c>
+      <c r="M8" s="13">
+        <v>280.10000000000002</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.75">
+      <c r="A9" s="13" t="s">
+        <v>54</v>
+      </c>
+      <c r="B9" s="13" t="s">
+        <v>46</v>
+      </c>
+      <c r="C9" s="13" t="s">
+        <v>116</v>
+      </c>
+      <c r="D9" s="13" t="s">
+        <v>31</v>
+      </c>
+      <c r="E9" s="13">
+        <v>247.80000305175781</v>
+      </c>
+      <c r="F9" s="13">
+        <v>232.5</v>
+      </c>
+      <c r="G9" s="13"/>
+      <c r="H9" s="13" t="s">
+        <v>261</v>
+      </c>
+      <c r="I9" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="J9" s="13"/>
+      <c r="K9" s="13">
+        <v>173.6</v>
+      </c>
+      <c r="L9" s="13">
+        <v>247.9</v>
+      </c>
+      <c r="M9" s="13">
+        <v>322.3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.75">
+      <c r="A10" s="13" t="s">
+        <v>57</v>
+      </c>
+      <c r="B10" s="13" t="s">
+        <v>58</v>
+      </c>
+      <c r="C10" s="13" t="s">
+        <v>111</v>
+      </c>
+      <c r="D10" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="E10" s="13">
+        <v>236.8999938964844</v>
+      </c>
+      <c r="F10" s="13">
+        <v>248.5</v>
+      </c>
+      <c r="G10" s="13"/>
+      <c r="H10" s="13" t="s">
+        <v>209</v>
+      </c>
+      <c r="I10" s="14" t="s">
+        <v>26</v>
+      </c>
+      <c r="J10" s="13"/>
+      <c r="K10" s="13">
+        <v>161.4</v>
+      </c>
+      <c r="L10" s="13">
+        <v>237.2</v>
+      </c>
+      <c r="M10" s="13">
+        <v>312.89999999999998</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.75">
+      <c r="A11" s="13" t="s">
+        <v>133</v>
+      </c>
+      <c r="B11" s="13" t="s">
+        <v>111</v>
+      </c>
+      <c r="C11" s="13" t="s">
+        <v>58</v>
+      </c>
+      <c r="D11" s="13" t="s">
+        <v>31</v>
+      </c>
+      <c r="E11" s="13">
+        <v>238.6000061035156</v>
+      </c>
+      <c r="F11" s="13">
+        <v>219.5</v>
+      </c>
+      <c r="G11" s="13"/>
+      <c r="H11" s="13" t="s">
+        <v>245</v>
+      </c>
+      <c r="I11" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="J11" s="13"/>
+      <c r="K11" s="13">
+        <v>163.80000000000001</v>
+      </c>
+      <c r="L11" s="13">
+        <v>239</v>
+      </c>
+      <c r="M11" s="13">
+        <v>313.10000000000002</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.75">
+      <c r="A12" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="B12" s="13" t="s">
+        <v>40</v>
+      </c>
+      <c r="C12" s="13" t="s">
+        <v>100</v>
+      </c>
+      <c r="D12" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="E12" s="13">
+        <v>246.80000305175781</v>
+      </c>
+      <c r="F12" s="13">
+        <v>241.5</v>
+      </c>
+      <c r="G12" s="13"/>
+      <c r="H12" s="13" t="s">
+        <v>244</v>
+      </c>
+      <c r="I12" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="J12" s="13"/>
+      <c r="K12" s="13">
+        <v>172.1</v>
+      </c>
+      <c r="L12" s="13">
+        <v>246.3</v>
+      </c>
+      <c r="M12" s="13">
+        <v>322.3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.75">
+      <c r="A13" s="13" t="s">
+        <v>84</v>
+      </c>
+      <c r="B13" s="13" t="s">
+        <v>85</v>
+      </c>
+      <c r="C13" s="13" t="s">
+        <v>64</v>
+      </c>
+      <c r="D13" s="13" t="s">
+        <v>31</v>
+      </c>
+      <c r="E13" s="13">
+        <v>240.8999938964844</v>
+      </c>
+      <c r="F13" s="13">
+        <v>230.5</v>
+      </c>
+      <c r="G13" s="13"/>
+      <c r="H13" s="13" t="s">
+        <v>282</v>
+      </c>
+      <c r="I13" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="J13" s="13"/>
+      <c r="K13" s="13">
+        <v>164</v>
+      </c>
+      <c r="L13" s="13">
+        <v>240.1</v>
+      </c>
+      <c r="M13" s="13">
+        <v>316.10000000000002</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.75">
+      <c r="A14" s="13" t="s">
+        <v>103</v>
+      </c>
+      <c r="B14" s="13" t="s">
+        <v>69</v>
+      </c>
+      <c r="C14" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="D14" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="E14" s="13">
+        <v>241.3999938964844</v>
+      </c>
+      <c r="F14" s="13">
+        <v>248.5</v>
+      </c>
+      <c r="G14" s="13"/>
+      <c r="H14" s="13" t="s">
+        <v>193</v>
+      </c>
+      <c r="I14" s="14" t="s">
+        <v>26</v>
+      </c>
+      <c r="J14" s="13"/>
+      <c r="K14" s="13">
+        <v>165.4</v>
+      </c>
+      <c r="L14" s="13">
+        <v>240.3</v>
+      </c>
+      <c r="M14" s="13">
+        <v>315.5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.75">
+      <c r="A15" s="13" t="s">
+        <v>119</v>
+      </c>
+      <c r="B15" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="C15" s="13" t="s">
+        <v>69</v>
+      </c>
+      <c r="D15" s="13" t="s">
+        <v>31</v>
+      </c>
+      <c r="E15" s="13">
+        <v>252.3999938964844</v>
+      </c>
+      <c r="F15" s="13">
+        <v>238.5</v>
+      </c>
+      <c r="G15" s="13"/>
+      <c r="H15" s="13" t="s">
+        <v>283</v>
+      </c>
+      <c r="I15" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="J15" s="13"/>
+      <c r="K15" s="13">
+        <v>175.4</v>
+      </c>
+      <c r="L15" s="13">
+        <v>252</v>
+      </c>
+      <c r="M15" s="13">
+        <v>327.7</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.75">
+      <c r="A16" s="13" t="s">
+        <v>109</v>
+      </c>
+      <c r="B16" s="13" t="s">
+        <v>110</v>
+      </c>
+      <c r="C16" s="13" t="s">
+        <v>35</v>
+      </c>
+      <c r="D16" s="13" t="s">
+        <v>31</v>
+      </c>
+      <c r="E16" s="13">
+        <v>232.3999938964844</v>
+      </c>
+      <c r="F16" s="13">
+        <v>222.5</v>
+      </c>
+      <c r="G16" s="13"/>
+      <c r="H16" s="13" t="s">
+        <v>214</v>
+      </c>
+      <c r="I16" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="J16" s="13"/>
+      <c r="K16" s="13">
+        <v>157.5</v>
+      </c>
+      <c r="L16" s="13">
+        <v>233.2</v>
+      </c>
+      <c r="M16" s="13">
+        <v>309.5</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" x14ac:dyDescent="0.75">
+      <c r="A17" s="13" t="s">
+        <v>62</v>
+      </c>
+      <c r="B17" s="13" t="s">
+        <v>63</v>
+      </c>
+      <c r="C17" s="13" t="s">
+        <v>41</v>
+      </c>
+      <c r="D17" s="13" t="s">
+        <v>31</v>
+      </c>
+      <c r="E17" s="13">
+        <v>226.8999938964844</v>
+      </c>
+      <c r="F17" s="13">
+        <v>211.5</v>
+      </c>
+      <c r="G17" s="13"/>
+      <c r="H17" s="13" t="s">
+        <v>284</v>
+      </c>
+      <c r="I17" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="J17" s="13"/>
+      <c r="K17" s="13">
+        <v>152.5</v>
+      </c>
+      <c r="L17" s="13">
+        <v>227.8</v>
+      </c>
+      <c r="M17" s="13">
+        <v>303.2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" x14ac:dyDescent="0.75">
+      <c r="A18" s="13" t="s">
+        <v>67</v>
+      </c>
+      <c r="B18" s="13" t="s">
+        <v>68</v>
+      </c>
+      <c r="C18" s="13" t="s">
+        <v>99</v>
+      </c>
+      <c r="D18" s="13" t="s">
+        <v>31</v>
+      </c>
+      <c r="E18" s="13">
+        <v>251</v>
+      </c>
+      <c r="F18" s="13">
+        <v>230.5</v>
+      </c>
+      <c r="G18" s="13"/>
+      <c r="H18" s="13" t="s">
+        <v>245</v>
+      </c>
+      <c r="I18" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="J18" s="13"/>
+      <c r="K18" s="13">
+        <v>173.9</v>
+      </c>
+      <c r="L18" s="13">
+        <v>250</v>
+      </c>
+      <c r="M18" s="13">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" x14ac:dyDescent="0.75">
+      <c r="A19" s="13" t="s">
+        <v>128</v>
+      </c>
+      <c r="B19" s="13" t="s">
+        <v>100</v>
+      </c>
+      <c r="C19" s="13" t="s">
+        <v>40</v>
+      </c>
+      <c r="D19" s="13" t="s">
+        <v>31</v>
+      </c>
+      <c r="E19" s="13">
+        <v>222.8999938964844</v>
+      </c>
+      <c r="F19" s="13">
+        <v>210.5</v>
+      </c>
+      <c r="G19" s="13"/>
+      <c r="H19" s="13" t="s">
+        <v>160</v>
+      </c>
+      <c r="I19" s="21" t="s">
+        <v>19</v>
+      </c>
+      <c r="J19" s="13"/>
+      <c r="K19" s="13">
+        <v>147.9</v>
+      </c>
+      <c r="L19" s="13">
+        <v>222.3</v>
+      </c>
+      <c r="M19" s="13">
+        <v>297.5</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
